--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:13:57+00:00</t>
+    <t>2023-06-15T09:14:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Practitioner.meta.extension:as-data-trace</t>
-  </si>
-  <si>
-    <t>as-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t>Practitioner.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-15T09:14:52+00:00</t>
+    <t>2023-06-16T14:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1092,7 +1092,7 @@
     <t>Need to know how to reach a practitioner independent to any roles the practitioner may have.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:code}
+    <t xml:space="preserve">profile:$this.resolve()}
 </t>
   </si>
   <si>
@@ -2312,7 +2312,7 @@
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="97.73828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="14.46484375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-16T14:16:48+00:00</t>
+    <t>2023-07-03T12:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-03T12:37:47+00:00</t>
+    <t>2023-07-10T14:48:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6578" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="625">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T14:48:30+00:00</t>
+    <t>2023-07-10T14:51:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,13 +493,10 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Nationalité de la personne.</t>
+    <t>[Donnée restreinte] : Nationalité de la personne (Synonyme : nationalite).</t>
   </si>
   <si>
     <t>Nationalité du professionnel</t>
-  </si>
-  <si>
-    <t>Synonyme : nationalite</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-frpractitioner-authorization</t>
@@ -528,13 +525,10 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Code officiel géographique (COG) de la commune (France) ou du pays</t>
+    <t>[Donnée restreinte] : Code officiel géographique (COG) de la commune (France) ou du pays (Synonyme : lieuNaissance).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du lieu de naissance du professionnel (Practitioner).</t>
-  </si>
-  <si>
-    <t>Synonyme : lieuNaissance</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-practitioner-deceased-date-time</t>
@@ -547,13 +541,10 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de décès de la personne.</t>
+    <t>[Donnée restreinte] : Date de décès de la personne (Synonyme : dateDeces).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date de décès du professionnel (Date of death of the practitioner if applicable).</t>
-  </si>
-  <si>
-    <t>Synonyme : dateDeces</t>
   </si>
   <si>
     <t>Practitioner.modifierExtension</t>
@@ -879,13 +870,13 @@
     <t>Practitioner.active</t>
   </si>
   <si>
-    <t>Le professionnel est-il actif? active | inactive</t>
+    <t>Le professionnel est-il actif? active | inactive. true  par défaut; false pour les professionnels supprimés</t>
   </si>
   <si>
     <t>Whether this practitioner's record is in active use.</t>
   </si>
   <si>
-    <t>true  par défaut; false pour les professionnels supprimés</t>
+    <t>If the practitioner is not in use by one organization, then it should mark the period on the PractitonerRole with an end date (even if they are active) as they may be active in another role.</t>
   </si>
   <si>
     <t>Need to be able to mark a practitioner record as not to be used because it was created in error.</t>
@@ -901,7 +892,7 @@
 </t>
   </si>
   <si>
-    <t>Une instance pour le nom d’usage et une instance pour le nom issu de l’état-civil</t>
+    <t>Une instance pour le nom d’usage et une instance pour le nom issu de l’état-civil. « usual » pour nom et prénom d’usage (Personne) ; « official » pour nom de famille et prénoms (Etat-civil)</t>
   </si>
   <si>
     <t>A human's name with the ability to identify parts and usage.</t>
@@ -944,7 +935,7 @@
     <t>Identifies the purpose for this name.</t>
   </si>
   <si>
-    <t>« usual » pour nom et prénom d’usage (Personne) ; « official » pour nom de famille et prénoms (Etat-civil)</t>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
@@ -1018,13 +1009,10 @@
     <t>Practitioner.name.prefix</t>
   </si>
   <si>
-    <t>Civilité de la personne physique.</t>
+    <t>Civilité de la personne physique (Synonyme : civilite).</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
-  </si>
-  <si>
-    <t>Synonyme : civilite</t>
   </si>
   <si>
     <t>Civilités des personnes physiques du RASS</t>
@@ -1273,13 +1261,13 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Adresse(s) de correspondance permettant de contacter le professionnel.</t>
+    <t>[Donnée restreinte] : Adresse(s) de correspondance permettant de contacter le professionnel (Synonyme : adresseCorrespondance).</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Synonyme : adresseCorrespondance</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
@@ -1288,13 +1276,10 @@
     <t>Practitioner.gender</t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Sexe administratif de la personne physique, au sens de l'état civil, masculin ou féminin.</t>
+    <t>[Donnée restreinte] : Sexe administratif de la personne physique, au sens de l'état civil, masculin ou féminin (Synonyme : sexeAdministratif).</t>
   </si>
   <si>
     <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
-  </si>
-  <si>
-    <t>Synonyme : sexeAdministratif</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
@@ -1313,13 +1298,10 @@
 </t>
   </si>
   <si>
-    <t>[Donnée restreinte] : Date de naissance de la personne, modifiée selon les règles du RNIV dans le cas des dates exceptionnelles.</t>
+    <t>[Donnée restreinte] : Date de naissance de la personne, modifiée selon les règles du RNIV dans le cas des dates exceptionnelles (Synonyme : dateNaissance).</t>
   </si>
   <si>
     <t>The date of birth for the practitioner.</t>
-  </si>
-  <si>
-    <t>Synonyme : dateNaissance</t>
   </si>
   <si>
     <t>Needed for identification.</t>
@@ -1919,10 +1901,7 @@
     <t>degreeType</t>
   </si>
   <si>
-    <t>Type de diplôme, par exemple : DE, DES, CES, etc.</t>
-  </si>
-  <si>
-    <t>typeDiplome</t>
+    <t>Type de diplôme, par exemple : DE, DES, CES, etc. (typeDiplome)</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
@@ -1962,13 +1941,10 @@
 </t>
   </si>
   <si>
-    <t>Langue parlée.</t>
+    <t>Langue parlée (Synonyme : langueParlee).</t>
   </si>
   <si>
     <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Synonyme : langueParlee</t>
   </si>
   <si>
     <t>Knowing which language a practitioner speaks can help in facilitating communication with patients.</t>
@@ -4088,9 +4064,7 @@
       <c r="M18" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>35</v>
@@ -4156,13 +4130,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>35</v>
@@ -4184,13 +4158,13 @@
         <v>35</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4258,13 +4232,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>35</v>
@@ -4286,17 +4260,15 @@
         <v>35</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>35</v>
@@ -4362,13 +4334,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>35</v>
@@ -4390,17 +4362,15 @@
         <v>35</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>35</v>
@@ -4466,10 +4436,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4495,16 +4465,16 @@
         <v>62</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>65</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
@@ -4553,7 +4523,7 @@
         <v>68</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4570,10 +4540,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4596,17 +4566,17 @@
         <v>43</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
@@ -4655,7 +4625,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4672,10 +4642,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4772,10 +4742,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4874,10 +4844,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4903,16 +4873,16 @@
         <v>123</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>35</v>
@@ -4937,31 +4907,31 @@
         <v>35</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -4978,10 +4948,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5004,19 +4974,19 @@
         <v>43</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>35</v>
@@ -5045,7 +5015,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>35</v>
@@ -5063,7 +5033,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -5080,10 +5050,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5180,10 +5150,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5282,10 +5252,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5311,16 +5281,16 @@
         <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>35</v>
@@ -5369,7 +5339,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5386,10 +5356,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5486,10 +5456,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5588,10 +5558,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5617,16 +5587,16 @@
         <v>89</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>35</v>
@@ -5639,7 +5609,7 @@
         <v>35</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>35</v>
@@ -5675,7 +5645,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -5692,10 +5662,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5721,13 +5691,13 @@
         <v>56</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5777,7 +5747,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5794,10 +5764,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5823,16 +5793,16 @@
         <v>123</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>35</v>
@@ -5881,7 +5851,7 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5898,10 +5868,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5927,16 +5897,16 @@
         <v>56</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>35</v>
@@ -5985,7 +5955,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -6002,10 +5972,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6028,19 +5998,19 @@
         <v>43</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>35</v>
@@ -6089,7 +6059,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -6106,10 +6076,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6135,16 +6105,16 @@
         <v>56</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>35</v>
@@ -6193,7 +6163,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6210,10 +6180,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6239,16 +6209,16 @@
         <v>89</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>35</v>
@@ -6261,7 +6231,7 @@
         <v>35</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>35</v>
@@ -6297,7 +6267,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -6314,10 +6284,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6343,13 +6313,13 @@
         <v>56</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6363,7 +6333,7 @@
         <v>35</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>35</v>
@@ -6399,7 +6369,7 @@
         <v>35</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -6416,10 +6386,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6442,16 +6412,16 @@
         <v>43</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6501,7 +6471,7 @@
         <v>35</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -6513,15 +6483,15 @@
         <v>54</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6544,16 +6514,16 @@
         <v>43</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6603,7 +6573,7 @@
         <v>35</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -6615,15 +6585,15 @@
         <v>54</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6646,26 +6616,26 @@
         <v>43</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="P43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q43" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q43" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="R43" t="s" s="2">
         <v>35</v>
       </c>
@@ -6709,7 +6679,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6726,10 +6696,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6752,19 +6722,19 @@
         <v>43</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>35</v>
@@ -6813,7 +6783,7 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -6830,10 +6800,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6930,10 +6900,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7032,13 +7002,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>61</v>
@@ -7060,13 +7030,13 @@
         <v>35</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>65</v>
@@ -7136,10 +7106,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7165,16 +7135,16 @@
         <v>123</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>35</v>
@@ -7199,13 +7169,13 @@
         <v>35</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>35</v>
@@ -7223,7 +7193,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7240,10 +7210,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7269,16 +7239,16 @@
         <v>56</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>35</v>
@@ -7327,7 +7297,7 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7344,14 +7314,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7373,13 +7343,13 @@
         <v>56</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7429,7 +7399,7 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7446,14 +7416,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7475,13 +7445,13 @@
         <v>56</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7531,7 +7501,7 @@
         <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -7548,10 +7518,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7577,13 +7547,13 @@
         <v>56</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>321</v>
+        <v>222</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7609,13 +7579,13 @@
         <v>35</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>35</v>
@@ -7633,7 +7603,7 @@
         <v>35</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7650,10 +7620,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7679,13 +7649,13 @@
         <v>56</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7714,10 +7684,10 @@
         <v>105</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>35</v>
@@ -7735,7 +7705,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7752,10 +7722,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7778,19 +7748,19 @@
         <v>43</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
@@ -7839,7 +7809,7 @@
         <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -7851,15 +7821,15 @@
         <v>54</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7882,19 +7852,19 @@
         <v>43</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -7931,7 +7901,7 @@
         <v>35</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
@@ -7941,7 +7911,7 @@
         <v>68</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -7953,15 +7923,15 @@
         <v>54</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8058,10 +8028,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8160,13 +8130,13 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>61</v>
@@ -8188,13 +8158,13 @@
         <v>35</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>65</v>
@@ -8264,10 +8234,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8293,13 +8263,13 @@
         <v>123</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8313,52 +8283,52 @@
         <v>35</v>
       </c>
       <c r="T59" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI59" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>81</v>
@@ -8366,10 +8336,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8395,16 +8365,16 @@
         <v>56</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>35</v>
@@ -8453,7 +8423,7 @@
         <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
@@ -8470,10 +8440,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8499,16 +8469,16 @@
         <v>123</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>35</v>
@@ -8533,13 +8503,13 @@
         <v>35</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>35</v>
@@ -8557,7 +8527,7 @@
         <v>35</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -8574,10 +8544,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8600,16 +8570,16 @@
         <v>43</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8659,7 +8629,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8676,10 +8646,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8702,16 +8672,16 @@
         <v>43</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8761,7 +8731,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -8773,18 +8743,18 @@
         <v>54</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>35</v>
@@ -8806,19 +8776,19 @@
         <v>35</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>35</v>
@@ -8867,7 +8837,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -8879,15 +8849,15 @@
         <v>54</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8984,10 +8954,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9086,13 +9056,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>61</v>
@@ -9114,13 +9084,13 @@
         <v>35</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>65</v>
@@ -9190,10 +9160,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9219,13 +9189,13 @@
         <v>123</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9239,52 +9209,52 @@
         <v>35</v>
       </c>
       <c r="T68" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI68" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>81</v>
@@ -9292,10 +9262,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9321,16 +9291,16 @@
         <v>56</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>35</v>
@@ -9379,7 +9349,7 @@
         <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -9396,10 +9366,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9425,16 +9395,16 @@
         <v>123</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>35</v>
@@ -9459,13 +9429,13 @@
         <v>35</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>35</v>
@@ -9483,7 +9453,7 @@
         <v>35</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -9500,10 +9470,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9526,16 +9496,16 @@
         <v>43</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9585,7 +9555,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -9602,10 +9572,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9628,16 +9598,16 @@
         <v>43</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9687,7 +9657,7 @@
         <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -9699,15 +9669,15 @@
         <v>54</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9730,19 +9700,19 @@
         <v>35</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>35</v>
@@ -9791,7 +9761,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -9808,10 +9778,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9837,16 +9807,16 @@
         <v>123</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>408</v>
+        <v>222</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>35</v>
@@ -9871,13 +9841,13 @@
         <v>35</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>35</v>
@@ -9895,7 +9865,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -9912,10 +9882,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9938,19 +9908,17 @@
         <v>43</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>35</v>
@@ -9999,7 +9967,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -10016,10 +9984,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10042,19 +10010,19 @@
         <v>35</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>35</v>
@@ -10103,7 +10071,7 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -10115,15 +10083,15 @@
         <v>54</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10146,13 +10114,13 @@
         <v>35</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10203,7 +10171,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -10220,10 +10188,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10320,10 +10288,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10422,14 +10390,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10451,16 +10419,16 @@
         <v>62</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>65</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>35</v>
@@ -10509,7 +10477,7 @@
         <v>35</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -10526,10 +10494,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10552,17 +10520,17 @@
         <v>35</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>35</v>
@@ -10611,7 +10579,7 @@
         <v>35</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -10628,10 +10596,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10654,16 +10622,16 @@
         <v>35</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -10692,10 +10660,10 @@
         <v>113</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>35</v>
@@ -10713,7 +10681,7 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>42</v>
@@ -10730,10 +10698,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10830,10 +10798,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10932,10 +10900,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10961,16 +10929,16 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O85" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>35</v>
@@ -11007,7 +10975,7 @@
         <v>35</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
@@ -11017,7 +10985,7 @@
         <v>68</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>36</v>
@@ -11034,13 +11002,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>35</v>
@@ -11065,16 +11033,16 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>35</v>
@@ -11099,11 +11067,11 @@
         <v>35</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>35</v>
@@ -11121,7 +11089,7 @@
         <v>35</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>36</v>
@@ -11138,10 +11106,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11238,10 +11206,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11340,10 +11308,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11369,23 +11337,23 @@
         <v>89</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>35</v>
@@ -11427,7 +11395,7 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
@@ -11444,10 +11412,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11473,13 +11441,13 @@
         <v>56</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11529,7 +11497,7 @@
         <v>35</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
@@ -11546,10 +11514,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11575,16 +11543,16 @@
         <v>123</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>35</v>
@@ -11633,7 +11601,7 @@
         <v>35</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
@@ -11650,10 +11618,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11679,16 +11647,16 @@
         <v>56</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>35</v>
@@ -11737,7 +11705,7 @@
         <v>35</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
@@ -11754,10 +11722,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11780,19 +11748,19 @@
         <v>43</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>35</v>
@@ -11841,7 +11809,7 @@
         <v>35</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -11858,13 +11826,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>35</v>
@@ -11889,16 +11857,16 @@
         <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
@@ -11923,11 +11891,11 @@
         <v>35</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>35</v>
@@ -11945,7 +11913,7 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
@@ -11962,10 +11930,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12062,10 +12030,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12164,10 +12132,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12193,23 +12161,23 @@
         <v>89</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>35</v>
@@ -12251,7 +12219,7 @@
         <v>35</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
@@ -12268,10 +12236,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12297,13 +12265,13 @@
         <v>56</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12353,7 +12321,7 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -12370,10 +12338,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12399,16 +12367,16 @@
         <v>123</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O99" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>35</v>
@@ -12457,7 +12425,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12474,10 +12442,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12503,16 +12471,16 @@
         <v>56</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>35</v>
@@ -12561,7 +12529,7 @@
         <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
@@ -12578,10 +12546,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12604,19 +12572,19 @@
         <v>43</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>35</v>
@@ -12665,7 +12633,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12682,13 +12650,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>35</v>
@@ -12713,16 +12681,16 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
@@ -12747,11 +12715,11 @@
         <v>35</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>35</v>
@@ -12769,7 +12737,7 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
@@ -12786,10 +12754,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12886,10 +12854,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12988,10 +12956,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13017,23 +12985,23 @@
         <v>89</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>35</v>
@@ -13075,7 +13043,7 @@
         <v>35</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
@@ -13092,10 +13060,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13121,13 +13089,13 @@
         <v>56</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13177,7 +13145,7 @@
         <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
@@ -13194,10 +13162,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13223,16 +13191,16 @@
         <v>123</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>35</v>
@@ -13281,7 +13249,7 @@
         <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
@@ -13298,10 +13266,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13327,16 +13295,16 @@
         <v>56</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>35</v>
@@ -13385,7 +13353,7 @@
         <v>35</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
@@ -13402,10 +13370,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13428,19 +13396,19 @@
         <v>43</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>35</v>
@@ -13489,7 +13457,7 @@
         <v>35</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13506,13 +13474,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>35</v>
@@ -13537,16 +13505,16 @@
         <v>101</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>35</v>
@@ -13571,11 +13539,11 @@
         <v>35</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>35</v>
@@ -13593,7 +13561,7 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>
@@ -13610,10 +13578,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13710,10 +13678,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13812,10 +13780,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13841,23 +13809,23 @@
         <v>89</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>35</v>
@@ -13899,7 +13867,7 @@
         <v>35</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>36</v>
@@ -13916,10 +13884,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13945,13 +13913,13 @@
         <v>56</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -14001,7 +13969,7 @@
         <v>35</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>36</v>
@@ -14018,10 +13986,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14047,16 +14015,16 @@
         <v>123</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O115" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>35</v>
@@ -14105,7 +14073,7 @@
         <v>35</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>36</v>
@@ -14122,10 +14090,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14151,16 +14119,16 @@
         <v>56</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>35</v>
@@ -14209,7 +14177,7 @@
         <v>35</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>36</v>
@@ -14226,10 +14194,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14252,19 +14220,19 @@
         <v>43</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="O117" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>35</v>
@@ -14313,7 +14281,7 @@
         <v>35</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>36</v>
@@ -14330,13 +14298,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>35</v>
@@ -14361,16 +14329,16 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O118" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>35</v>
@@ -14395,11 +14363,11 @@
         <v>35</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>35</v>
@@ -14417,7 +14385,7 @@
         <v>35</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>36</v>
@@ -14434,10 +14402,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14534,10 +14502,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14636,10 +14604,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14665,23 +14633,23 @@
         <v>89</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>35</v>
@@ -14723,7 +14691,7 @@
         <v>35</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>36</v>
@@ -14740,10 +14708,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14769,13 +14737,13 @@
         <v>56</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14825,7 +14793,7 @@
         <v>35</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>36</v>
@@ -14842,10 +14810,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14871,16 +14839,16 @@
         <v>123</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O123" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>35</v>
@@ -14929,7 +14897,7 @@
         <v>35</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>36</v>
@@ -14946,10 +14914,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14975,16 +14943,16 @@
         <v>56</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>35</v>
@@ -15033,7 +15001,7 @@
         <v>35</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>36</v>
@@ -15050,10 +15018,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15076,19 +15044,19 @@
         <v>43</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>35</v>
@@ -15137,7 +15105,7 @@
         <v>35</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>36</v>
@@ -15154,13 +15122,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>35</v>
@@ -15185,16 +15153,16 @@
         <v>101</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O126" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>35</v>
@@ -15219,11 +15187,11 @@
         <v>35</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>35</v>
@@ -15241,7 +15209,7 @@
         <v>35</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>36</v>
@@ -15258,10 +15226,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15358,10 +15326,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15460,10 +15428,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15489,23 +15457,23 @@
         <v>89</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>35</v>
@@ -15547,7 +15515,7 @@
         <v>35</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>36</v>
@@ -15564,10 +15532,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15593,13 +15561,13 @@
         <v>56</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -15649,7 +15617,7 @@
         <v>35</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>36</v>
@@ -15666,10 +15634,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15695,16 +15663,16 @@
         <v>123</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O131" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>35</v>
@@ -15753,7 +15721,7 @@
         <v>35</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>36</v>
@@ -15770,10 +15738,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15799,16 +15767,16 @@
         <v>56</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>35</v>
@@ -15857,7 +15825,7 @@
         <v>35</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>36</v>
@@ -15874,10 +15842,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15900,19 +15868,19 @@
         <v>43</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>35</v>
@@ -15961,7 +15929,7 @@
         <v>35</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>36</v>
@@ -15978,13 +15946,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>35</v>
@@ -16009,16 +15977,16 @@
         <v>101</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O134" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>35</v>
@@ -16043,11 +16011,11 @@
         <v>35</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y134" s="2"/>
       <c r="Z134" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>35</v>
@@ -16065,7 +16033,7 @@
         <v>35</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>36</v>
@@ -16082,10 +16050,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16182,10 +16150,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16284,10 +16252,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16313,23 +16281,23 @@
         <v>89</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>35</v>
@@ -16371,7 +16339,7 @@
         <v>35</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>36</v>
@@ -16388,10 +16356,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16417,13 +16385,13 @@
         <v>56</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -16473,7 +16441,7 @@
         <v>35</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>36</v>
@@ -16490,10 +16458,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16519,16 +16487,16 @@
         <v>123</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O139" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>35</v>
@@ -16577,7 +16545,7 @@
         <v>35</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>36</v>
@@ -16594,10 +16562,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16623,16 +16591,16 @@
         <v>56</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>35</v>
@@ -16681,7 +16649,7 @@
         <v>35</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>36</v>
@@ -16698,10 +16666,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16724,19 +16692,19 @@
         <v>43</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N141" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>35</v>
@@ -16785,7 +16753,7 @@
         <v>35</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>36</v>
@@ -16802,13 +16770,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>35</v>
@@ -16833,16 +16801,16 @@
         <v>101</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O142" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>35</v>
@@ -16867,11 +16835,11 @@
         <v>35</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>35</v>
@@ -16889,7 +16857,7 @@
         <v>35</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>36</v>
@@ -16906,10 +16874,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17006,10 +16974,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17108,10 +17076,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17137,23 +17105,23 @@
         <v>89</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>35</v>
@@ -17195,7 +17163,7 @@
         <v>35</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>36</v>
@@ -17212,10 +17180,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17241,13 +17209,13 @@
         <v>56</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17297,7 +17265,7 @@
         <v>35</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>36</v>
@@ -17314,10 +17282,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17343,16 +17311,16 @@
         <v>123</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O147" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>35</v>
@@ -17401,7 +17369,7 @@
         <v>35</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>36</v>
@@ -17418,10 +17386,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17447,16 +17415,16 @@
         <v>56</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>35</v>
@@ -17505,7 +17473,7 @@
         <v>35</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>36</v>
@@ -17522,10 +17490,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17548,19 +17516,19 @@
         <v>43</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>35</v>
@@ -17609,7 +17577,7 @@
         <v>35</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>36</v>
@@ -17626,13 +17594,13 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>35</v>
@@ -17657,16 +17625,16 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O150" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>35</v>
@@ -17691,11 +17659,11 @@
         <v>35</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>35</v>
@@ -17713,7 +17681,7 @@
         <v>35</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>36</v>
@@ -17730,10 +17698,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17830,10 +17798,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17932,10 +17900,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17961,23 +17929,23 @@
         <v>89</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>35</v>
@@ -18019,7 +17987,7 @@
         <v>35</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>36</v>
@@ -18036,10 +18004,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18065,13 +18033,13 @@
         <v>56</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18121,7 +18089,7 @@
         <v>35</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>36</v>
@@ -18138,10 +18106,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18167,16 +18135,16 @@
         <v>123</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O155" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>35</v>
@@ -18225,7 +18193,7 @@
         <v>35</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>36</v>
@@ -18242,10 +18210,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18271,16 +18239,16 @@
         <v>56</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>35</v>
@@ -18329,7 +18297,7 @@
         <v>35</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>36</v>
@@ -18346,10 +18314,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18372,19 +18340,19 @@
         <v>43</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>35</v>
@@ -18433,7 +18401,7 @@
         <v>35</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>36</v>
@@ -18450,13 +18418,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>35</v>
@@ -18481,16 +18449,16 @@
         <v>101</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O158" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>35</v>
@@ -18515,11 +18483,11 @@
         <v>35</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y158" s="2"/>
       <c r="Z158" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>35</v>
@@ -18537,7 +18505,7 @@
         <v>35</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>36</v>
@@ -18554,10 +18522,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18654,10 +18622,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18756,10 +18724,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18785,23 +18753,23 @@
         <v>89</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>35</v>
@@ -18843,7 +18811,7 @@
         <v>35</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>36</v>
@@ -18860,10 +18828,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18889,13 +18857,13 @@
         <v>56</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -18945,7 +18913,7 @@
         <v>35</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>36</v>
@@ -18962,10 +18930,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18991,16 +18959,16 @@
         <v>123</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O163" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>35</v>
@@ -19049,7 +19017,7 @@
         <v>35</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>36</v>
@@ -19066,10 +19034,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19095,16 +19063,16 @@
         <v>56</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>35</v>
@@ -19153,7 +19121,7 @@
         <v>35</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>36</v>
@@ -19170,10 +19138,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19196,19 +19164,19 @@
         <v>43</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>35</v>
@@ -19257,7 +19225,7 @@
         <v>35</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>36</v>
@@ -19274,13 +19242,13 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>35</v>
@@ -19305,16 +19273,16 @@
         <v>101</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O166" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>35</v>
@@ -19339,11 +19307,11 @@
         <v>35</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>35</v>
@@ -19361,7 +19329,7 @@
         <v>35</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>36</v>
@@ -19378,10 +19346,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19478,10 +19446,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19580,10 +19548,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19609,23 +19577,23 @@
         <v>89</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>35</v>
@@ -19667,7 +19635,7 @@
         <v>35</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>36</v>
@@ -19684,10 +19652,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19713,13 +19681,13 @@
         <v>56</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -19769,7 +19737,7 @@
         <v>35</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>36</v>
@@ -19786,10 +19754,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19815,16 +19783,16 @@
         <v>123</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O171" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>35</v>
@@ -19873,7 +19841,7 @@
         <v>35</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>36</v>
@@ -19890,10 +19858,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19919,16 +19887,16 @@
         <v>56</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>35</v>
@@ -19977,7 +19945,7 @@
         <v>35</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>36</v>
@@ -19994,10 +19962,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20020,19 +19988,19 @@
         <v>43</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N173" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>35</v>
@@ -20081,7 +20049,7 @@
         <v>35</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>36</v>
@@ -20098,13 +20066,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>35</v>
@@ -20129,16 +20097,16 @@
         <v>101</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O174" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>35</v>
@@ -20163,11 +20131,11 @@
         <v>35</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>35</v>
@@ -20185,7 +20153,7 @@
         <v>35</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>36</v>
@@ -20202,10 +20170,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20302,10 +20270,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20404,10 +20372,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20433,23 +20401,23 @@
         <v>89</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>35</v>
@@ -20491,7 +20459,7 @@
         <v>35</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>36</v>
@@ -20508,10 +20476,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20537,13 +20505,13 @@
         <v>56</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -20593,7 +20561,7 @@
         <v>35</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>36</v>
@@ -20610,10 +20578,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20639,16 +20607,16 @@
         <v>123</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O179" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>35</v>
@@ -20697,7 +20665,7 @@
         <v>35</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>36</v>
@@ -20714,10 +20682,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20743,16 +20711,16 @@
         <v>56</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>35</v>
@@ -20801,7 +20769,7 @@
         <v>35</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>36</v>
@@ -20818,10 +20786,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20844,19 +20812,19 @@
         <v>43</v>
       </c>
       <c r="K181" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N181" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>35</v>
@@ -20905,7 +20873,7 @@
         <v>35</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>36</v>
@@ -20922,13 +20890,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>35</v>
@@ -20953,16 +20921,16 @@
         <v>101</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O182" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>35</v>
@@ -20987,11 +20955,11 @@
         <v>35</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>35</v>
@@ -21009,7 +20977,7 @@
         <v>35</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>36</v>
@@ -21026,10 +20994,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21126,10 +21094,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21228,10 +21196,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21257,23 +21225,23 @@
         <v>89</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>35</v>
@@ -21315,7 +21283,7 @@
         <v>35</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>36</v>
@@ -21332,10 +21300,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21361,13 +21329,13 @@
         <v>56</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -21417,7 +21385,7 @@
         <v>35</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>36</v>
@@ -21434,10 +21402,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21463,16 +21431,16 @@
         <v>123</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O187" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>35</v>
@@ -21521,7 +21489,7 @@
         <v>35</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>36</v>
@@ -21538,10 +21506,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21567,16 +21535,16 @@
         <v>56</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>35</v>
@@ -21625,7 +21593,7 @@
         <v>35</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>36</v>
@@ -21642,10 +21610,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21668,19 +21636,19 @@
         <v>43</v>
       </c>
       <c r="K189" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N189" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L189" t="s" s="2">
+      <c r="O189" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>35</v>
@@ -21729,7 +21697,7 @@
         <v>35</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>36</v>
@@ -21746,13 +21714,13 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>35</v>
@@ -21777,16 +21745,16 @@
         <v>101</v>
       </c>
       <c r="L190" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O190" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>35</v>
@@ -21811,11 +21779,11 @@
         <v>35</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>35</v>
@@ -21833,7 +21801,7 @@
         <v>35</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>36</v>
@@ -21850,10 +21818,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21950,10 +21918,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -22052,10 +22020,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22081,23 +22049,23 @@
         <v>89</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q193" s="2"/>
       <c r="R193" t="s" s="2">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="S193" t="s" s="2">
         <v>35</v>
@@ -22139,7 +22107,7 @@
         <v>35</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>36</v>
@@ -22156,10 +22124,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22185,13 +22153,13 @@
         <v>56</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -22241,7 +22209,7 @@
         <v>35</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>36</v>
@@ -22258,10 +22226,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22287,16 +22255,16 @@
         <v>123</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O195" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>35</v>
@@ -22345,7 +22313,7 @@
         <v>35</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>36</v>
@@ -22362,10 +22330,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22391,16 +22359,16 @@
         <v>56</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>35</v>
@@ -22449,7 +22417,7 @@
         <v>35</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>36</v>
@@ -22466,10 +22434,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22492,19 +22460,19 @@
         <v>43</v>
       </c>
       <c r="K197" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L197" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M197" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N197" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L197" t="s" s="2">
+      <c r="O197" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>35</v>
@@ -22553,7 +22521,7 @@
         <v>35</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>36</v>
@@ -22570,13 +22538,13 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>35</v>
@@ -22601,16 +22569,16 @@
         <v>101</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>615</v>
+        <v>202</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>35</v>
@@ -22635,11 +22603,11 @@
         <v>35</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>35</v>
@@ -22657,7 +22625,7 @@
         <v>35</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>36</v>
@@ -22674,10 +22642,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22703,16 +22671,16 @@
         <v>56</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M199" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O199" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>35</v>
@@ -22761,7 +22729,7 @@
         <v>35</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>36</v>
@@ -22778,10 +22746,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22804,19 +22772,19 @@
         <v>35</v>
       </c>
       <c r="K200" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L200" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M200" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N200" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L200" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="O200" t="s" s="2">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>35</v>
@@ -22865,7 +22833,7 @@
         <v>35</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>36</v>
@@ -22877,15 +22845,15 @@
         <v>54</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22908,16 +22876,16 @@
         <v>35</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -22967,7 +22935,7 @@
         <v>35</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>36</v>
@@ -22979,15 +22947,15 @@
         <v>54</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -23010,19 +22978,19 @@
         <v>35</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>630</v>
+        <v>437</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>35</v>
@@ -23047,11 +23015,11 @@
         <v>35</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>35</v>
@@ -23069,7 +23037,7 @@
         <v>35</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1715,7 +1715,7 @@
 </t>
   </si>
   <si>
-    <t>Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
+    <t>[Donnée restreinte] : telecommunication. Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
   </si>
   <si>
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
@@ -1760,13 +1760,10 @@
     <t>Practitioner.telecom.system</t>
   </si>
   <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
+    <t>« phone » pour Téléphone et Téléphone 2 ; « fax » pour Télécopie ; « email » pour adresse e-mail</t>
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>« phone » pour Téléphone et Téléphone 2 ; « fax » pour Télécopie ; « email » pour adresse e-mail</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/contact-point-system</t>
@@ -1897,6 +1894,9 @@
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.system</t>
+  </si>
+  <si>
+    <t>phone | fax | email | pager | url | sms | other</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.value</t>
@@ -20812,7 +20812,7 @@
         <v>556</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>557</v>
+        <v>356</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -20826,7 +20826,7 @@
         <v>73</v>
       </c>
       <c r="T163" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="U163" t="s" s="2">
         <v>73</v>
@@ -20841,37 +20841,37 @@
         <v>318</v>
       </c>
       <c r="Y163" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z163" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z163" t="s" s="2">
+      <c r="AA163" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF163" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AA163" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF163" t="s" s="2">
+      <c r="AG163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI163" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AG163" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI163" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>94</v>
@@ -20879,10 +20879,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20908,16 +20908,16 @@
         <v>96</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>73</v>
@@ -20966,7 +20966,7 @@
         <v>73</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>74</v>
@@ -20983,10 +20983,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21012,16 +21012,16 @@
         <v>162</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>73</v>
@@ -21049,28 +21049,28 @@
         <v>318</v>
       </c>
       <c r="Y165" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z165" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z165" t="s" s="2">
+      <c r="AA165" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF165" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>74</v>
@@ -21087,10 +21087,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21113,16 +21113,16 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L166" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="M166" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -21172,7 +21172,7 @@
         <v>73</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>74</v>
@@ -21189,10 +21189,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21218,10 +21218,10 @@
         <v>252</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N167" t="s" s="2">
         <v>393</v>
@@ -21274,7 +21274,7 @@
         <v>73</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>74</v>
@@ -21291,13 +21291,13 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>539</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>73</v>
@@ -21319,10 +21319,10 @@
         <v>73</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="M168" t="s" s="2">
         <v>542</v>
@@ -21397,7 +21397,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>547</v>
@@ -21497,7 +21497,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>548</v>
@@ -21599,7 +21599,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>548</v>
@@ -21701,13 +21701,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>548</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>73</v>
@@ -21729,13 +21729,13 @@
         <v>73</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21803,7 +21803,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>554</v>
@@ -21832,7 +21832,7 @@
         <v>162</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>555</v>
+        <v>599</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>556</v>
@@ -21852,7 +21852,7 @@
         <v>73</v>
       </c>
       <c r="T173" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="U173" t="s" s="2">
         <v>73</v>
@@ -21867,37 +21867,37 @@
         <v>318</v>
       </c>
       <c r="Y173" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z173" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z173" t="s" s="2">
+      <c r="AA173" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF173" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AA173" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF173" t="s" s="2">
+      <c r="AG173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI173" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AG173" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI173" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>94</v>
@@ -21908,7 +21908,7 @@
         <v>600</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21934,16 +21934,16 @@
         <v>96</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>73</v>
@@ -21992,7 +21992,7 @@
         <v>73</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>74</v>
@@ -22012,7 +22012,7 @@
         <v>601</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22038,16 +22038,16 @@
         <v>162</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>602</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>73</v>
@@ -22075,28 +22075,28 @@
         <v>318</v>
       </c>
       <c r="Y175" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z175" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z175" t="s" s="2">
+      <c r="AA175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF175" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>74</v>
@@ -22116,7 +22116,7 @@
         <v>603</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22139,16 +22139,16 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -22198,7 +22198,7 @@
         <v>73</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>74</v>
@@ -22218,7 +22218,7 @@
         <v>604</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22244,10 +22244,10 @@
         <v>252</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>393</v>
@@ -22300,7 +22300,7 @@
         <v>73</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>74</v>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22465" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22466" uniqueCount="1250">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1883,14 +1883,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
     <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.system</t>
@@ -21608,7 +21601,7 @@
         <v>550</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -21635,7 +21628,9 @@
       <c r="M171" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N171" s="2"/>
+      <c r="N171" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>73</v>
@@ -21717,7 +21712,7 @@
         <v>74</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>82</v>
@@ -21729,13 +21724,13 @@
         <v>73</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="L172" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="M172" t="s" s="2">
-        <v>597</v>
+        <v>214</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21803,7 +21798,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>554</v>
@@ -21832,7 +21827,7 @@
         <v>162</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>556</v>
@@ -21905,7 +21900,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>562</v>
@@ -22009,7 +22004,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>568</v>
@@ -22044,7 +22039,7 @@
         <v>570</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="O175" t="s" s="2">
         <v>572</v>
@@ -22113,7 +22108,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>576</v>
@@ -22215,7 +22210,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>582</v>
@@ -22317,10 +22312,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22343,19 +22338,19 @@
         <v>73</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>73</v>
@@ -22404,7 +22399,7 @@
         <v>73</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>74</v>
@@ -22421,10 +22416,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22450,16 +22445,16 @@
         <v>162</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>356</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>73</v>
@@ -22487,10 +22482,10 @@
         <v>318</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>73</v>
@@ -22508,7 +22503,7 @@
         <v>73</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>74</v>
@@ -22525,10 +22520,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22551,17 +22546,17 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>73</v>
@@ -22610,7 +22605,7 @@
         <v>73</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>74</v>
@@ -22627,10 +22622,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22656,16 +22651,16 @@
         <v>292</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N181" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>73</v>
@@ -22714,7 +22709,7 @@
         <v>73</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>74</v>
@@ -22726,15 +22721,15 @@
         <v>93</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22757,13 +22752,13 @@
         <v>73</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -22802,7 +22797,7 @@
         <v>73</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AC182" s="2"/>
       <c r="AD182" t="s" s="2">
@@ -22812,7 +22807,7 @@
         <v>108</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>74</v>
@@ -22829,10 +22824,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22929,10 +22924,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23031,14 +23026,14 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
@@ -23060,10 +23055,10 @@
         <v>102</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N185" t="s" s="2">
         <v>105</v>
@@ -23118,7 +23113,7 @@
         <v>73</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>74</v>
@@ -23135,10 +23130,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23164,14 +23159,14 @@
         <v>305</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>73</v>
@@ -23220,7 +23215,7 @@
         <v>73</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>74</v>
@@ -23237,10 +23232,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23266,13 +23261,13 @@
         <v>323</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -23301,10 +23296,10 @@
         <v>152</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>73</v>
@@ -23322,7 +23317,7 @@
         <v>73</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -23339,10 +23334,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23439,10 +23434,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -23541,10 +23536,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23616,7 +23611,7 @@
         <v>73</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AC190" s="2"/>
       <c r="AD190" t="s" s="2">
@@ -23643,13 +23638,13 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>73</v>
@@ -23712,7 +23707,7 @@
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>73</v>
@@ -23747,10 +23742,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23847,10 +23842,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23949,10 +23944,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -23978,7 +23973,7 @@
         <v>128</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M194" t="s" s="2">
         <v>343</v>
@@ -23994,7 +23989,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>73</v>
@@ -24053,10 +24048,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24155,10 +24150,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24259,10 +24254,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24363,10 +24358,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24467,13 +24462,13 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D199" t="s" s="2">
         <v>73</v>
@@ -24536,7 +24531,7 @@
       </c>
       <c r="Y199" s="2"/>
       <c r="Z199" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>73</v>
@@ -24571,10 +24566,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24671,10 +24666,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24773,10 +24768,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24802,7 +24797,7 @@
         <v>128</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>343</v>
@@ -24818,7 +24813,7 @@
       </c>
       <c r="Q202" s="2"/>
       <c r="R202" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S202" t="s" s="2">
         <v>73</v>
@@ -24877,10 +24872,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -24979,10 +24974,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25083,10 +25078,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25187,10 +25182,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25291,13 +25286,13 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>73</v>
@@ -25360,7 +25355,7 @@
       </c>
       <c r="Y207" s="2"/>
       <c r="Z207" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA207" t="s" s="2">
         <v>73</v>
@@ -25395,10 +25390,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25495,10 +25490,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25597,10 +25592,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25626,7 +25621,7 @@
         <v>128</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="M210" t="s" s="2">
         <v>343</v>
@@ -25642,7 +25637,7 @@
       </c>
       <c r="Q210" s="2"/>
       <c r="R210" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S210" t="s" s="2">
         <v>73</v>
@@ -25701,10 +25696,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -25803,10 +25798,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -25907,10 +25902,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26011,10 +26006,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26115,13 +26110,13 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D215" t="s" s="2">
         <v>73</v>
@@ -26184,7 +26179,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>73</v>
@@ -26219,10 +26214,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -26319,10 +26314,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -26421,10 +26416,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -26450,10 +26445,10 @@
         <v>128</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N218" t="s" s="2">
         <v>344</v>
@@ -26466,7 +26461,7 @@
       </c>
       <c r="Q218" s="2"/>
       <c r="R218" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="S218" t="s" s="2">
         <v>73</v>
@@ -26525,10 +26520,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -26627,10 +26622,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -26731,10 +26726,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -26835,10 +26830,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -26939,13 +26934,13 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D223" t="s" s="2">
         <v>73</v>
@@ -27008,7 +27003,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>73</v>
@@ -27043,10 +27038,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -27143,10 +27138,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -27245,10 +27240,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -27274,7 +27269,7 @@
         <v>128</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="M226" t="s" s="2">
         <v>343</v>
@@ -27290,7 +27285,7 @@
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="S226" t="s" s="2">
         <v>73</v>
@@ -27349,10 +27344,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -27451,10 +27446,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -27555,10 +27550,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -27659,10 +27654,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -27763,13 +27758,13 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D231" t="s" s="2">
         <v>73</v>
@@ -27832,7 +27827,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>73</v>
@@ -27867,10 +27862,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -27967,10 +27962,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -28069,10 +28064,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -28098,7 +28093,7 @@
         <v>128</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M234" t="s" s="2">
         <v>343</v>
@@ -28114,7 +28109,7 @@
       </c>
       <c r="Q234" s="2"/>
       <c r="R234" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="S234" t="s" s="2">
         <v>73</v>
@@ -28173,10 +28168,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -28275,10 +28270,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -28379,10 +28374,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -28483,10 +28478,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -28587,13 +28582,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>73</v>
@@ -28656,7 +28651,7 @@
       </c>
       <c r="Y239" s="2"/>
       <c r="Z239" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>73</v>
@@ -28691,10 +28686,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -28791,10 +28786,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -28893,10 +28888,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -28922,7 +28917,7 @@
         <v>128</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="M242" t="s" s="2">
         <v>343</v>
@@ -28938,7 +28933,7 @@
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="S242" t="s" s="2">
         <v>73</v>
@@ -28997,10 +28992,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -29099,10 +29094,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -29203,10 +29198,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -29307,10 +29302,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -29411,13 +29406,13 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D247" t="s" s="2">
         <v>73</v>
@@ -29480,7 +29475,7 @@
       </c>
       <c r="Y247" s="2"/>
       <c r="Z247" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>73</v>
@@ -29515,10 +29510,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -29615,10 +29610,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -29717,10 +29712,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -29746,7 +29741,7 @@
         <v>128</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M250" t="s" s="2">
         <v>343</v>
@@ -29762,7 +29757,7 @@
       </c>
       <c r="Q250" s="2"/>
       <c r="R250" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="S250" t="s" s="2">
         <v>73</v>
@@ -29821,10 +29816,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -29923,10 +29918,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -30027,10 +30022,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -30131,10 +30126,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -30235,13 +30230,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>73</v>
@@ -30304,7 +30299,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>73</v>
@@ -30339,10 +30334,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -30439,10 +30434,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -30541,10 +30536,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -30570,10 +30565,10 @@
         <v>128</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="N258" t="s" s="2">
         <v>344</v>
@@ -30586,7 +30581,7 @@
       </c>
       <c r="Q258" s="2"/>
       <c r="R258" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="S258" t="s" s="2">
         <v>73</v>
@@ -30645,10 +30640,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -30747,10 +30742,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -30851,10 +30846,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -30955,10 +30950,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -31059,13 +31054,13 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D263" t="s" s="2">
         <v>73</v>
@@ -31128,7 +31123,7 @@
       </c>
       <c r="Y263" s="2"/>
       <c r="Z263" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>73</v>
@@ -31163,10 +31158,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -31263,10 +31258,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -31365,10 +31360,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -31394,10 +31389,10 @@
         <v>128</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="N266" t="s" s="2">
         <v>344</v>
@@ -31410,7 +31405,7 @@
       </c>
       <c r="Q266" s="2"/>
       <c r="R266" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="S266" t="s" s="2">
         <v>73</v>
@@ -31469,10 +31464,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -31571,10 +31566,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -31675,10 +31670,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -31779,10 +31774,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -31883,13 +31878,13 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D271" t="s" s="2">
         <v>73</v>
@@ -31952,7 +31947,7 @@
       </c>
       <c r="Y271" s="2"/>
       <c r="Z271" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA271" t="s" s="2">
         <v>73</v>
@@ -31987,10 +31982,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -32087,10 +32082,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -32189,10 +32184,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -32218,7 +32213,7 @@
         <v>128</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>343</v>
@@ -32234,7 +32229,7 @@
       </c>
       <c r="Q274" s="2"/>
       <c r="R274" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S274" t="s" s="2">
         <v>73</v>
@@ -32293,10 +32288,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -32395,10 +32390,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -32499,10 +32494,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -32603,10 +32598,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -32707,13 +32702,13 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D279" t="s" s="2">
         <v>73</v>
@@ -32776,7 +32771,7 @@
       </c>
       <c r="Y279" s="2"/>
       <c r="Z279" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA279" t="s" s="2">
         <v>73</v>
@@ -32811,10 +32806,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -32911,10 +32906,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -33013,10 +33008,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -33042,10 +33037,10 @@
         <v>128</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="N282" t="s" s="2">
         <v>344</v>
@@ -33058,7 +33053,7 @@
       </c>
       <c r="Q282" s="2"/>
       <c r="R282" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="S282" t="s" s="2">
         <v>73</v>
@@ -33117,10 +33112,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -33219,10 +33214,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -33323,10 +33318,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -33427,10 +33422,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -33531,13 +33526,13 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D287" t="s" s="2">
         <v>73</v>
@@ -33600,7 +33595,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>73</v>
@@ -33635,10 +33630,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -33735,10 +33730,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -33837,10 +33832,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -33866,10 +33861,10 @@
         <v>128</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N290" t="s" s="2">
         <v>344</v>
@@ -33882,7 +33877,7 @@
       </c>
       <c r="Q290" s="2"/>
       <c r="R290" t="s" s="2">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="S290" t="s" s="2">
         <v>73</v>
@@ -33941,10 +33936,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -34043,10 +34038,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -34147,10 +34142,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -34251,10 +34246,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -34355,13 +34350,13 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D295" t="s" s="2">
         <v>73</v>
@@ -34424,7 +34419,7 @@
       </c>
       <c r="Y295" s="2"/>
       <c r="Z295" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA295" t="s" s="2">
         <v>73</v>
@@ -34459,10 +34454,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -34559,10 +34554,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -34661,10 +34656,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -34690,7 +34685,7 @@
         <v>128</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>343</v>
@@ -34706,7 +34701,7 @@
       </c>
       <c r="Q298" s="2"/>
       <c r="R298" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="S298" t="s" s="2">
         <v>73</v>
@@ -34765,10 +34760,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -34867,10 +34862,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -34971,10 +34966,10 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -35075,10 +35070,10 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -35179,10 +35174,10 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -35283,10 +35278,10 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -35312,16 +35307,16 @@
         <v>252</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N304" t="s" s="2">
         <v>393</v>
       </c>
       <c r="O304" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="P304" t="s" s="2">
         <v>73</v>
@@ -35370,7 +35365,7 @@
         <v>73</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>74</v>
@@ -35387,10 +35382,10 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -35416,13 +35411,13 @@
         <v>397</v>
       </c>
       <c r="L305" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M305" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="N305" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="M305" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="N305" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="O305" s="2"/>
       <c r="P305" t="s" s="2">
@@ -35472,7 +35467,7 @@
         <v>73</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>74</v>
@@ -35489,13 +35484,13 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D306" t="s" s="2">
         <v>73</v>
@@ -35517,13 +35512,13 @@
         <v>73</v>
       </c>
       <c r="K306" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L306" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M306" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="L306" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="M306" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N306" s="2"/>
       <c r="O306" s="2"/>
@@ -35574,7 +35569,7 @@
         <v>73</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>74</v>
@@ -35591,10 +35586,10 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
@@ -35691,10 +35686,10 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -35793,13 +35788,13 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D309" t="s" s="2">
         <v>73</v>
@@ -35821,13 +35816,13 @@
         <v>73</v>
       </c>
       <c r="K309" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="L309" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="M309" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="L309" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="M309" t="s" s="2">
-        <v>834</v>
       </c>
       <c r="N309" s="2"/>
       <c r="O309" s="2"/>
@@ -35895,14 +35890,14 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E310" s="2"/>
       <c r="F310" t="s" s="2">
@@ -35924,10 +35919,10 @@
         <v>102</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N310" t="s" s="2">
         <v>105</v>
@@ -35982,7 +35977,7 @@
         <v>73</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>74</v>
@@ -35999,10 +35994,10 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
@@ -36028,14 +36023,14 @@
         <v>305</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="N311" s="2"/>
       <c r="O311" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P311" t="s" s="2">
         <v>73</v>
@@ -36084,7 +36079,7 @@
         <v>73</v>
       </c>
       <c r="AF311" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AG311" t="s" s="2">
         <v>74</v>
@@ -36101,10 +36096,10 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -36130,13 +36125,13 @@
         <v>323</v>
       </c>
       <c r="L312" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M312" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N312" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M312" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N312" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" t="s" s="2">
@@ -36165,10 +36160,10 @@
         <v>152</v>
       </c>
       <c r="Y312" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="Z312" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AA312" t="s" s="2">
         <v>73</v>
@@ -36186,7 +36181,7 @@
         <v>73</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>81</v>
@@ -36203,10 +36198,10 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -36303,10 +36298,10 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -36405,10 +36400,10 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -36480,14 +36475,14 @@
         <v>73</v>
       </c>
       <c r="AB315" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AC315" s="2"/>
       <c r="AD315" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE315" t="s" s="2">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AF315" t="s" s="2">
         <v>338</v>
@@ -36507,13 +36502,13 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D316" t="s" s="2">
         <v>73</v>
@@ -36576,7 +36571,7 @@
       </c>
       <c r="Y316" s="2"/>
       <c r="Z316" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA316" t="s" s="2">
         <v>73</v>
@@ -36611,10 +36606,10 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -36711,10 +36706,10 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
@@ -36813,10 +36808,10 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
@@ -36842,7 +36837,7 @@
         <v>128</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M319" t="s" s="2">
         <v>343</v>
@@ -36858,7 +36853,7 @@
       </c>
       <c r="Q319" s="2"/>
       <c r="R319" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S319" t="s" s="2">
         <v>73</v>
@@ -36917,10 +36912,10 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
@@ -37019,10 +37014,10 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
@@ -37123,10 +37118,10 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
@@ -37227,10 +37222,10 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
@@ -37331,13 +37326,13 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D324" t="s" s="2">
         <v>73</v>
@@ -37400,7 +37395,7 @@
       </c>
       <c r="Y324" s="2"/>
       <c r="Z324" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA324" t="s" s="2">
         <v>73</v>
@@ -37435,10 +37430,10 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" t="s" s="2">
@@ -37535,10 +37530,10 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" t="s" s="2">
@@ -37637,10 +37632,10 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
@@ -37666,7 +37661,7 @@
         <v>128</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="M327" t="s" s="2">
         <v>343</v>
@@ -37682,7 +37677,7 @@
       </c>
       <c r="Q327" s="2"/>
       <c r="R327" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S327" t="s" s="2">
         <v>73</v>
@@ -37741,10 +37736,10 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
@@ -37843,10 +37838,10 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" t="s" s="2">
@@ -37947,10 +37942,10 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" t="s" s="2">
@@ -38051,10 +38046,10 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
@@ -38155,13 +38150,13 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D332" t="s" s="2">
         <v>73</v>
@@ -38224,7 +38219,7 @@
       </c>
       <c r="Y332" s="2"/>
       <c r="Z332" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA332" t="s" s="2">
         <v>73</v>
@@ -38259,10 +38254,10 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
@@ -38359,10 +38354,10 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" t="s" s="2">
@@ -38461,10 +38456,10 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
@@ -38490,7 +38485,7 @@
         <v>128</v>
       </c>
       <c r="L335" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="M335" t="s" s="2">
         <v>343</v>
@@ -38506,7 +38501,7 @@
       </c>
       <c r="Q335" s="2"/>
       <c r="R335" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S335" t="s" s="2">
         <v>73</v>
@@ -38565,10 +38560,10 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" t="s" s="2">
@@ -38667,10 +38662,10 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
@@ -38771,10 +38766,10 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
@@ -38875,10 +38870,10 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -38979,13 +38974,13 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D340" t="s" s="2">
         <v>73</v>
@@ -39048,7 +39043,7 @@
       </c>
       <c r="Y340" s="2"/>
       <c r="Z340" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA340" t="s" s="2">
         <v>73</v>
@@ -39083,10 +39078,10 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
@@ -39183,10 +39178,10 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
@@ -39285,10 +39280,10 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
@@ -39314,10 +39309,10 @@
         <v>128</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N343" t="s" s="2">
         <v>344</v>
@@ -39330,7 +39325,7 @@
       </c>
       <c r="Q343" s="2"/>
       <c r="R343" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="S343" t="s" s="2">
         <v>73</v>
@@ -39389,10 +39384,10 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" t="s" s="2">
@@ -39491,10 +39486,10 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
@@ -39595,10 +39590,10 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" t="s" s="2">
@@ -39699,10 +39694,10 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" t="s" s="2">
@@ -39803,13 +39798,13 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D348" t="s" s="2">
         <v>73</v>
@@ -39872,7 +39867,7 @@
       </c>
       <c r="Y348" s="2"/>
       <c r="Z348" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA348" t="s" s="2">
         <v>73</v>
@@ -39907,10 +39902,10 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" t="s" s="2">
@@ -40007,10 +40002,10 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" t="s" s="2">
@@ -40109,10 +40104,10 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" t="s" s="2">
@@ -40138,7 +40133,7 @@
         <v>128</v>
       </c>
       <c r="L351" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="M351" t="s" s="2">
         <v>343</v>
@@ -40154,7 +40149,7 @@
       </c>
       <c r="Q351" s="2"/>
       <c r="R351" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="S351" t="s" s="2">
         <v>73</v>
@@ -40213,10 +40208,10 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" t="s" s="2">
@@ -40315,10 +40310,10 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" t="s" s="2">
@@ -40419,10 +40414,10 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" t="s" s="2">
@@ -40523,10 +40518,10 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" t="s" s="2">
@@ -40627,13 +40622,13 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D356" t="s" s="2">
         <v>73</v>
@@ -40696,7 +40691,7 @@
       </c>
       <c r="Y356" s="2"/>
       <c r="Z356" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA356" t="s" s="2">
         <v>73</v>
@@ -40731,10 +40726,10 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" t="s" s="2">
@@ -40831,10 +40826,10 @@
     </row>
     <row r="358" hidden="true">
       <c r="A358" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C358" s="2"/>
       <c r="D358" t="s" s="2">
@@ -40933,10 +40928,10 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C359" s="2"/>
       <c r="D359" t="s" s="2">
@@ -40962,7 +40957,7 @@
         <v>128</v>
       </c>
       <c r="L359" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M359" t="s" s="2">
         <v>343</v>
@@ -40978,7 +40973,7 @@
       </c>
       <c r="Q359" s="2"/>
       <c r="R359" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="S359" t="s" s="2">
         <v>73</v>
@@ -41037,10 +41032,10 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C360" s="2"/>
       <c r="D360" t="s" s="2">
@@ -41139,10 +41134,10 @@
     </row>
     <row r="361" hidden="true">
       <c r="A361" t="s" s="2">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C361" s="2"/>
       <c r="D361" t="s" s="2">
@@ -41243,10 +41238,10 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" t="s" s="2">
@@ -41347,10 +41342,10 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C363" s="2"/>
       <c r="D363" t="s" s="2">
@@ -41451,13 +41446,13 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D364" t="s" s="2">
         <v>73</v>
@@ -41520,7 +41515,7 @@
       </c>
       <c r="Y364" s="2"/>
       <c r="Z364" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA364" t="s" s="2">
         <v>73</v>
@@ -41555,10 +41550,10 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" t="s" s="2">
@@ -41655,10 +41650,10 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" t="s" s="2">
@@ -41757,10 +41752,10 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C367" s="2"/>
       <c r="D367" t="s" s="2">
@@ -41786,7 +41781,7 @@
         <v>128</v>
       </c>
       <c r="L367" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="M367" t="s" s="2">
         <v>343</v>
@@ -41802,7 +41797,7 @@
       </c>
       <c r="Q367" s="2"/>
       <c r="R367" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="S367" t="s" s="2">
         <v>73</v>
@@ -41861,10 +41856,10 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C368" s="2"/>
       <c r="D368" t="s" s="2">
@@ -41963,10 +41958,10 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" t="s" s="2">
@@ -42067,10 +42062,10 @@
     </row>
     <row r="370" hidden="true">
       <c r="A370" t="s" s="2">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C370" s="2"/>
       <c r="D370" t="s" s="2">
@@ -42171,10 +42166,10 @@
     </row>
     <row r="371" hidden="true">
       <c r="A371" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C371" s="2"/>
       <c r="D371" t="s" s="2">
@@ -42275,13 +42270,13 @@
     </row>
     <row r="372" hidden="true">
       <c r="A372" t="s" s="2">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D372" t="s" s="2">
         <v>73</v>
@@ -42344,7 +42339,7 @@
       </c>
       <c r="Y372" s="2"/>
       <c r="Z372" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA372" t="s" s="2">
         <v>73</v>
@@ -42379,10 +42374,10 @@
     </row>
     <row r="373" hidden="true">
       <c r="A373" t="s" s="2">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C373" s="2"/>
       <c r="D373" t="s" s="2">
@@ -42479,10 +42474,10 @@
     </row>
     <row r="374" hidden="true">
       <c r="A374" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C374" s="2"/>
       <c r="D374" t="s" s="2">
@@ -42581,10 +42576,10 @@
     </row>
     <row r="375" hidden="true">
       <c r="A375" t="s" s="2">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C375" s="2"/>
       <c r="D375" t="s" s="2">
@@ -42610,7 +42605,7 @@
         <v>128</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M375" t="s" s="2">
         <v>343</v>
@@ -42626,7 +42621,7 @@
       </c>
       <c r="Q375" s="2"/>
       <c r="R375" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="S375" t="s" s="2">
         <v>73</v>
@@ -42685,10 +42680,10 @@
     </row>
     <row r="376" hidden="true">
       <c r="A376" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C376" s="2"/>
       <c r="D376" t="s" s="2">
@@ -42787,10 +42782,10 @@
     </row>
     <row r="377" hidden="true">
       <c r="A377" t="s" s="2">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C377" s="2"/>
       <c r="D377" t="s" s="2">
@@ -42891,10 +42886,10 @@
     </row>
     <row r="378" hidden="true">
       <c r="A378" t="s" s="2">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C378" s="2"/>
       <c r="D378" t="s" s="2">
@@ -42995,10 +42990,10 @@
     </row>
     <row r="379" hidden="true">
       <c r="A379" t="s" s="2">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" t="s" s="2">
@@ -43099,13 +43094,13 @@
     </row>
     <row r="380" hidden="true">
       <c r="A380" t="s" s="2">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D380" t="s" s="2">
         <v>73</v>
@@ -43168,7 +43163,7 @@
       </c>
       <c r="Y380" s="2"/>
       <c r="Z380" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA380" t="s" s="2">
         <v>73</v>
@@ -43203,10 +43198,10 @@
     </row>
     <row r="381" hidden="true">
       <c r="A381" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" t="s" s="2">
@@ -43303,10 +43298,10 @@
     </row>
     <row r="382" hidden="true">
       <c r="A382" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" t="s" s="2">
@@ -43405,10 +43400,10 @@
     </row>
     <row r="383" hidden="true">
       <c r="A383" t="s" s="2">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" t="s" s="2">
@@ -43434,10 +43429,10 @@
         <v>128</v>
       </c>
       <c r="L383" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M383" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="N383" t="s" s="2">
         <v>344</v>
@@ -43450,7 +43445,7 @@
       </c>
       <c r="Q383" s="2"/>
       <c r="R383" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="S383" t="s" s="2">
         <v>73</v>
@@ -43509,10 +43504,10 @@
     </row>
     <row r="384" hidden="true">
       <c r="A384" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" t="s" s="2">
@@ -43611,10 +43606,10 @@
     </row>
     <row r="385" hidden="true">
       <c r="A385" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" t="s" s="2">
@@ -43715,10 +43710,10 @@
     </row>
     <row r="386" hidden="true">
       <c r="A386" t="s" s="2">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" t="s" s="2">
@@ -43819,10 +43814,10 @@
     </row>
     <row r="387" hidden="true">
       <c r="A387" t="s" s="2">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" t="s" s="2">
@@ -43923,13 +43918,13 @@
     </row>
     <row r="388" hidden="true">
       <c r="A388" t="s" s="2">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D388" t="s" s="2">
         <v>73</v>
@@ -43992,7 +43987,7 @@
       </c>
       <c r="Y388" s="2"/>
       <c r="Z388" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA388" t="s" s="2">
         <v>73</v>
@@ -44027,10 +44022,10 @@
     </row>
     <row r="389" hidden="true">
       <c r="A389" t="s" s="2">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C389" s="2"/>
       <c r="D389" t="s" s="2">
@@ -44127,10 +44122,10 @@
     </row>
     <row r="390" hidden="true">
       <c r="A390" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C390" s="2"/>
       <c r="D390" t="s" s="2">
@@ -44229,10 +44224,10 @@
     </row>
     <row r="391" hidden="true">
       <c r="A391" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C391" s="2"/>
       <c r="D391" t="s" s="2">
@@ -44258,10 +44253,10 @@
         <v>128</v>
       </c>
       <c r="L391" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M391" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="N391" t="s" s="2">
         <v>344</v>
@@ -44274,7 +44269,7 @@
       </c>
       <c r="Q391" s="2"/>
       <c r="R391" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="S391" t="s" s="2">
         <v>73</v>
@@ -44333,10 +44328,10 @@
     </row>
     <row r="392" hidden="true">
       <c r="A392" t="s" s="2">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C392" s="2"/>
       <c r="D392" t="s" s="2">
@@ -44435,10 +44430,10 @@
     </row>
     <row r="393" hidden="true">
       <c r="A393" t="s" s="2">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C393" s="2"/>
       <c r="D393" t="s" s="2">
@@ -44539,10 +44534,10 @@
     </row>
     <row r="394" hidden="true">
       <c r="A394" t="s" s="2">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C394" s="2"/>
       <c r="D394" t="s" s="2">
@@ -44643,10 +44638,10 @@
     </row>
     <row r="395" hidden="true">
       <c r="A395" t="s" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C395" s="2"/>
       <c r="D395" t="s" s="2">
@@ -44747,13 +44742,13 @@
     </row>
     <row r="396" hidden="true">
       <c r="A396" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D396" t="s" s="2">
         <v>73</v>
@@ -44816,7 +44811,7 @@
       </c>
       <c r="Y396" s="2"/>
       <c r="Z396" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA396" t="s" s="2">
         <v>73</v>
@@ -44851,10 +44846,10 @@
     </row>
     <row r="397" hidden="true">
       <c r="A397" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C397" s="2"/>
       <c r="D397" t="s" s="2">
@@ -44951,10 +44946,10 @@
     </row>
     <row r="398" hidden="true">
       <c r="A398" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C398" s="2"/>
       <c r="D398" t="s" s="2">
@@ -45053,10 +45048,10 @@
     </row>
     <row r="399" hidden="true">
       <c r="A399" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C399" s="2"/>
       <c r="D399" t="s" s="2">
@@ -45082,7 +45077,7 @@
         <v>128</v>
       </c>
       <c r="L399" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M399" t="s" s="2">
         <v>343</v>
@@ -45098,7 +45093,7 @@
       </c>
       <c r="Q399" s="2"/>
       <c r="R399" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S399" t="s" s="2">
         <v>73</v>
@@ -45157,10 +45152,10 @@
     </row>
     <row r="400" hidden="true">
       <c r="A400" t="s" s="2">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C400" s="2"/>
       <c r="D400" t="s" s="2">
@@ -45259,10 +45254,10 @@
     </row>
     <row r="401" hidden="true">
       <c r="A401" t="s" s="2">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C401" s="2"/>
       <c r="D401" t="s" s="2">
@@ -45363,10 +45358,10 @@
     </row>
     <row r="402" hidden="true">
       <c r="A402" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C402" s="2"/>
       <c r="D402" t="s" s="2">
@@ -45467,10 +45462,10 @@
     </row>
     <row r="403" hidden="true">
       <c r="A403" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" t="s" s="2">
@@ -45571,13 +45566,13 @@
     </row>
     <row r="404" hidden="true">
       <c r="A404" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D404" t="s" s="2">
         <v>73</v>
@@ -45640,7 +45635,7 @@
       </c>
       <c r="Y404" s="2"/>
       <c r="Z404" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA404" t="s" s="2">
         <v>73</v>
@@ -45675,10 +45670,10 @@
     </row>
     <row r="405" hidden="true">
       <c r="A405" t="s" s="2">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" t="s" s="2">
@@ -45775,10 +45770,10 @@
     </row>
     <row r="406" hidden="true">
       <c r="A406" t="s" s="2">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" t="s" s="2">
@@ -45877,10 +45872,10 @@
     </row>
     <row r="407" hidden="true">
       <c r="A407" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" t="s" s="2">
@@ -45906,10 +45901,10 @@
         <v>128</v>
       </c>
       <c r="L407" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M407" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="N407" t="s" s="2">
         <v>344</v>
@@ -45922,7 +45917,7 @@
       </c>
       <c r="Q407" s="2"/>
       <c r="R407" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="S407" t="s" s="2">
         <v>73</v>
@@ -45981,10 +45976,10 @@
     </row>
     <row r="408" hidden="true">
       <c r="A408" t="s" s="2">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" t="s" s="2">
@@ -46083,10 +46078,10 @@
     </row>
     <row r="409" hidden="true">
       <c r="A409" t="s" s="2">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" t="s" s="2">
@@ -46187,10 +46182,10 @@
     </row>
     <row r="410" hidden="true">
       <c r="A410" t="s" s="2">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C410" s="2"/>
       <c r="D410" t="s" s="2">
@@ -46291,10 +46286,10 @@
     </row>
     <row r="411" hidden="true">
       <c r="A411" t="s" s="2">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C411" s="2"/>
       <c r="D411" t="s" s="2">
@@ -46395,13 +46390,13 @@
     </row>
     <row r="412" hidden="true">
       <c r="A412" t="s" s="2">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D412" t="s" s="2">
         <v>73</v>
@@ -46464,7 +46459,7 @@
       </c>
       <c r="Y412" s="2"/>
       <c r="Z412" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA412" t="s" s="2">
         <v>73</v>
@@ -46499,10 +46494,10 @@
     </row>
     <row r="413" hidden="true">
       <c r="A413" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" t="s" s="2">
@@ -46599,10 +46594,10 @@
     </row>
     <row r="414" hidden="true">
       <c r="A414" t="s" s="2">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C414" s="2"/>
       <c r="D414" t="s" s="2">
@@ -46701,10 +46696,10 @@
     </row>
     <row r="415" hidden="true">
       <c r="A415" t="s" s="2">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" t="s" s="2">
@@ -46730,10 +46725,10 @@
         <v>128</v>
       </c>
       <c r="L415" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N415" t="s" s="2">
         <v>344</v>
@@ -46746,7 +46741,7 @@
       </c>
       <c r="Q415" s="2"/>
       <c r="R415" t="s" s="2">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="S415" t="s" s="2">
         <v>73</v>
@@ -46805,10 +46800,10 @@
     </row>
     <row r="416" hidden="true">
       <c r="A416" t="s" s="2">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C416" s="2"/>
       <c r="D416" t="s" s="2">
@@ -46907,10 +46902,10 @@
     </row>
     <row r="417" hidden="true">
       <c r="A417" t="s" s="2">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C417" s="2"/>
       <c r="D417" t="s" s="2">
@@ -47011,10 +47006,10 @@
     </row>
     <row r="418" hidden="true">
       <c r="A418" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C418" s="2"/>
       <c r="D418" t="s" s="2">
@@ -47115,10 +47110,10 @@
     </row>
     <row r="419" hidden="true">
       <c r="A419" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C419" s="2"/>
       <c r="D419" t="s" s="2">
@@ -47219,13 +47214,13 @@
     </row>
     <row r="420" hidden="true">
       <c r="A420" t="s" s="2">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D420" t="s" s="2">
         <v>73</v>
@@ -47288,7 +47283,7 @@
       </c>
       <c r="Y420" s="2"/>
       <c r="Z420" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA420" t="s" s="2">
         <v>73</v>
@@ -47323,10 +47318,10 @@
     </row>
     <row r="421" hidden="true">
       <c r="A421" t="s" s="2">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C421" s="2"/>
       <c r="D421" t="s" s="2">
@@ -47423,10 +47418,10 @@
     </row>
     <row r="422" hidden="true">
       <c r="A422" t="s" s="2">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" t="s" s="2">
@@ -47525,10 +47520,10 @@
     </row>
     <row r="423" hidden="true">
       <c r="A423" t="s" s="2">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C423" s="2"/>
       <c r="D423" t="s" s="2">
@@ -47554,7 +47549,7 @@
         <v>128</v>
       </c>
       <c r="L423" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="M423" t="s" s="2">
         <v>343</v>
@@ -47570,7 +47565,7 @@
       </c>
       <c r="Q423" s="2"/>
       <c r="R423" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="S423" t="s" s="2">
         <v>73</v>
@@ -47629,10 +47624,10 @@
     </row>
     <row r="424" hidden="true">
       <c r="A424" t="s" s="2">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" t="s" s="2">
@@ -47731,10 +47726,10 @@
     </row>
     <row r="425" hidden="true">
       <c r="A425" t="s" s="2">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C425" s="2"/>
       <c r="D425" t="s" s="2">
@@ -47835,10 +47830,10 @@
     </row>
     <row r="426" hidden="true">
       <c r="A426" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C426" s="2"/>
       <c r="D426" t="s" s="2">
@@ -47939,10 +47934,10 @@
     </row>
     <row r="427" hidden="true">
       <c r="A427" t="s" s="2">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C427" s="2"/>
       <c r="D427" t="s" s="2">
@@ -48043,13 +48038,13 @@
     </row>
     <row r="428" hidden="true">
       <c r="A428" t="s" s="2">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D428" t="s" s="2">
         <v>73</v>
@@ -48112,7 +48107,7 @@
       </c>
       <c r="Y428" s="2"/>
       <c r="Z428" t="s" s="2">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="AA428" t="s" s="2">
         <v>73</v>
@@ -48147,13 +48142,13 @@
     </row>
     <row r="429" hidden="true">
       <c r="A429" t="s" s="2">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D429" t="s" s="2">
         <v>73</v>
@@ -48216,7 +48211,7 @@
       </c>
       <c r="Y429" s="2"/>
       <c r="Z429" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA429" t="s" s="2">
         <v>73</v>
@@ -48251,10 +48246,10 @@
     </row>
     <row r="430" hidden="true">
       <c r="A430" t="s" s="2">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C430" s="2"/>
       <c r="D430" t="s" s="2">
@@ -48355,10 +48350,10 @@
     </row>
     <row r="431" hidden="true">
       <c r="A431" t="s" s="2">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C431" s="2"/>
       <c r="D431" t="s" s="2">
@@ -48384,16 +48379,16 @@
         <v>252</v>
       </c>
       <c r="L431" t="s" s="2">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="M431" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N431" t="s" s="2">
         <v>393</v>
       </c>
       <c r="O431" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="P431" t="s" s="2">
         <v>73</v>
@@ -48442,7 +48437,7 @@
         <v>73</v>
       </c>
       <c r="AF431" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AG431" t="s" s="2">
         <v>74</v>
@@ -48459,10 +48454,10 @@
     </row>
     <row r="432" hidden="true">
       <c r="A432" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C432" s="2"/>
       <c r="D432" t="s" s="2">
@@ -48559,10 +48554,10 @@
     </row>
     <row r="433" hidden="true">
       <c r="A433" t="s" s="2">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C433" s="2"/>
       <c r="D433" t="s" s="2">
@@ -48661,10 +48656,10 @@
     </row>
     <row r="434" hidden="true">
       <c r="A434" t="s" s="2">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C434" s="2"/>
       <c r="D434" t="s" s="2">
@@ -48690,7 +48685,7 @@
         <v>259</v>
       </c>
       <c r="L434" t="s" s="2">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="M434" t="s" s="2">
         <v>261</v>
@@ -48763,10 +48758,10 @@
     </row>
     <row r="435" hidden="true">
       <c r="A435" t="s" s="2">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C435" s="2"/>
       <c r="D435" t="s" s="2">
@@ -48792,7 +48787,7 @@
         <v>259</v>
       </c>
       <c r="L435" t="s" s="2">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="M435" t="s" s="2">
         <v>268</v>
@@ -48867,10 +48862,10 @@
     </row>
     <row r="436" hidden="true">
       <c r="A436" t="s" s="2">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C436" s="2"/>
       <c r="D436" t="s" s="2">
@@ -48893,16 +48888,16 @@
         <v>73</v>
       </c>
       <c r="K436" t="s" s="2">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="L436" t="s" s="2">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="M436" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="N436" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="O436" s="2"/>
       <c r="P436" t="s" s="2">
@@ -48952,7 +48947,7 @@
         <v>73</v>
       </c>
       <c r="AF436" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AG436" t="s" s="2">
         <v>74</v>
@@ -48969,13 +48964,13 @@
     </row>
     <row r="437" hidden="true">
       <c r="A437" t="s" s="2">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D437" t="s" s="2">
         <v>73</v>
@@ -48997,13 +48992,13 @@
         <v>73</v>
       </c>
       <c r="K437" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L437" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="M437" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="L437" t="s" s="2">
-        <v>976</v>
-      </c>
-      <c r="M437" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N437" s="2"/>
       <c r="O437" s="2"/>
@@ -49054,7 +49049,7 @@
         <v>73</v>
       </c>
       <c r="AF437" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG437" t="s" s="2">
         <v>74</v>
@@ -49071,10 +49066,10 @@
     </row>
     <row r="438" hidden="true">
       <c r="A438" t="s" s="2">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C438" s="2"/>
       <c r="D438" t="s" s="2">
@@ -49171,10 +49166,10 @@
     </row>
     <row r="439" hidden="true">
       <c r="A439" t="s" s="2">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C439" s="2"/>
       <c r="D439" t="s" s="2">
@@ -49273,14 +49268,14 @@
     </row>
     <row r="440" hidden="true">
       <c r="A440" t="s" s="2">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C440" s="2"/>
       <c r="D440" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E440" s="2"/>
       <c r="F440" t="s" s="2">
@@ -49302,10 +49297,10 @@
         <v>102</v>
       </c>
       <c r="L440" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="M440" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N440" t="s" s="2">
         <v>105</v>
@@ -49360,7 +49355,7 @@
         <v>73</v>
       </c>
       <c r="AF440" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AG440" t="s" s="2">
         <v>74</v>
@@ -49377,10 +49372,10 @@
     </row>
     <row r="441" hidden="true">
       <c r="A441" t="s" s="2">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C441" s="2"/>
       <c r="D441" t="s" s="2">
@@ -49406,14 +49401,14 @@
         <v>305</v>
       </c>
       <c r="L441" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M441" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="N441" s="2"/>
       <c r="O441" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P441" t="s" s="2">
         <v>73</v>
@@ -49462,7 +49457,7 @@
         <v>73</v>
       </c>
       <c r="AF441" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AG441" t="s" s="2">
         <v>74</v>
@@ -49479,10 +49474,10 @@
     </row>
     <row r="442" hidden="true">
       <c r="A442" t="s" s="2">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C442" s="2"/>
       <c r="D442" t="s" s="2">
@@ -49508,13 +49503,13 @@
         <v>323</v>
       </c>
       <c r="L442" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M442" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N442" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M442" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N442" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O442" s="2"/>
       <c r="P442" t="s" s="2">
@@ -49543,10 +49538,10 @@
         <v>152</v>
       </c>
       <c r="Y442" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="Z442" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AA442" t="s" s="2">
         <v>73</v>
@@ -49564,7 +49559,7 @@
         <v>73</v>
       </c>
       <c r="AF442" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG442" t="s" s="2">
         <v>81</v>
@@ -49581,10 +49576,10 @@
     </row>
     <row r="443" hidden="true">
       <c r="A443" t="s" s="2">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C443" s="2"/>
       <c r="D443" t="s" s="2">
@@ -49681,10 +49676,10 @@
     </row>
     <row r="444" hidden="true">
       <c r="A444" t="s" s="2">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C444" s="2"/>
       <c r="D444" t="s" s="2">
@@ -49783,10 +49778,10 @@
     </row>
     <row r="445" hidden="true">
       <c r="A445" t="s" s="2">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C445" s="2"/>
       <c r="D445" t="s" s="2">
@@ -49858,14 +49853,14 @@
         <v>73</v>
       </c>
       <c r="AB445" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AC445" s="2"/>
       <c r="AD445" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE445" t="s" s="2">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AF445" t="s" s="2">
         <v>338</v>
@@ -49885,13 +49880,13 @@
     </row>
     <row r="446" hidden="true">
       <c r="A446" t="s" s="2">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D446" t="s" s="2">
         <v>73</v>
@@ -49954,7 +49949,7 @@
       </c>
       <c r="Y446" s="2"/>
       <c r="Z446" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA446" t="s" s="2">
         <v>73</v>
@@ -49989,10 +49984,10 @@
     </row>
     <row r="447" hidden="true">
       <c r="A447" t="s" s="2">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C447" s="2"/>
       <c r="D447" t="s" s="2">
@@ -50089,10 +50084,10 @@
     </row>
     <row r="448" hidden="true">
       <c r="A448" t="s" s="2">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C448" s="2"/>
       <c r="D448" t="s" s="2">
@@ -50191,10 +50186,10 @@
     </row>
     <row r="449" hidden="true">
       <c r="A449" t="s" s="2">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C449" s="2"/>
       <c r="D449" t="s" s="2">
@@ -50220,7 +50215,7 @@
         <v>128</v>
       </c>
       <c r="L449" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M449" t="s" s="2">
         <v>343</v>
@@ -50236,7 +50231,7 @@
       </c>
       <c r="Q449" s="2"/>
       <c r="R449" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S449" t="s" s="2">
         <v>73</v>
@@ -50295,10 +50290,10 @@
     </row>
     <row r="450" hidden="true">
       <c r="A450" t="s" s="2">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C450" s="2"/>
       <c r="D450" t="s" s="2">
@@ -50397,10 +50392,10 @@
     </row>
     <row r="451" hidden="true">
       <c r="A451" t="s" s="2">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C451" s="2"/>
       <c r="D451" t="s" s="2">
@@ -50501,10 +50496,10 @@
     </row>
     <row r="452" hidden="true">
       <c r="A452" t="s" s="2">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C452" s="2"/>
       <c r="D452" t="s" s="2">
@@ -50605,10 +50600,10 @@
     </row>
     <row r="453" hidden="true">
       <c r="A453" t="s" s="2">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C453" s="2"/>
       <c r="D453" t="s" s="2">
@@ -50709,13 +50704,13 @@
     </row>
     <row r="454" hidden="true">
       <c r="A454" t="s" s="2">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D454" t="s" s="2">
         <v>73</v>
@@ -50778,7 +50773,7 @@
       </c>
       <c r="Y454" s="2"/>
       <c r="Z454" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA454" t="s" s="2">
         <v>73</v>
@@ -50813,10 +50808,10 @@
     </row>
     <row r="455" hidden="true">
       <c r="A455" t="s" s="2">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C455" s="2"/>
       <c r="D455" t="s" s="2">
@@ -50913,10 +50908,10 @@
     </row>
     <row r="456" hidden="true">
       <c r="A456" t="s" s="2">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C456" s="2"/>
       <c r="D456" t="s" s="2">
@@ -51015,10 +51010,10 @@
     </row>
     <row r="457" hidden="true">
       <c r="A457" t="s" s="2">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C457" s="2"/>
       <c r="D457" t="s" s="2">
@@ -51044,7 +51039,7 @@
         <v>128</v>
       </c>
       <c r="L457" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="M457" t="s" s="2">
         <v>343</v>
@@ -51060,7 +51055,7 @@
       </c>
       <c r="Q457" s="2"/>
       <c r="R457" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S457" t="s" s="2">
         <v>73</v>
@@ -51119,10 +51114,10 @@
     </row>
     <row r="458" hidden="true">
       <c r="A458" t="s" s="2">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C458" s="2"/>
       <c r="D458" t="s" s="2">
@@ -51221,10 +51216,10 @@
     </row>
     <row r="459" hidden="true">
       <c r="A459" t="s" s="2">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C459" s="2"/>
       <c r="D459" t="s" s="2">
@@ -51325,10 +51320,10 @@
     </row>
     <row r="460" hidden="true">
       <c r="A460" t="s" s="2">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C460" s="2"/>
       <c r="D460" t="s" s="2">
@@ -51429,10 +51424,10 @@
     </row>
     <row r="461" hidden="true">
       <c r="A461" t="s" s="2">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C461" s="2"/>
       <c r="D461" t="s" s="2">
@@ -51533,13 +51528,13 @@
     </row>
     <row r="462" hidden="true">
       <c r="A462" t="s" s="2">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D462" t="s" s="2">
         <v>73</v>
@@ -51602,7 +51597,7 @@
       </c>
       <c r="Y462" s="2"/>
       <c r="Z462" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA462" t="s" s="2">
         <v>73</v>
@@ -51637,10 +51632,10 @@
     </row>
     <row r="463" hidden="true">
       <c r="A463" t="s" s="2">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C463" s="2"/>
       <c r="D463" t="s" s="2">
@@ -51737,10 +51732,10 @@
     </row>
     <row r="464" hidden="true">
       <c r="A464" t="s" s="2">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C464" s="2"/>
       <c r="D464" t="s" s="2">
@@ -51839,10 +51834,10 @@
     </row>
     <row r="465" hidden="true">
       <c r="A465" t="s" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C465" s="2"/>
       <c r="D465" t="s" s="2">
@@ -51868,7 +51863,7 @@
         <v>128</v>
       </c>
       <c r="L465" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="M465" t="s" s="2">
         <v>343</v>
@@ -51884,7 +51879,7 @@
       </c>
       <c r="Q465" s="2"/>
       <c r="R465" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S465" t="s" s="2">
         <v>73</v>
@@ -51943,10 +51938,10 @@
     </row>
     <row r="466" hidden="true">
       <c r="A466" t="s" s="2">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C466" s="2"/>
       <c r="D466" t="s" s="2">
@@ -52045,10 +52040,10 @@
     </row>
     <row r="467" hidden="true">
       <c r="A467" t="s" s="2">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C467" s="2"/>
       <c r="D467" t="s" s="2">
@@ -52149,10 +52144,10 @@
     </row>
     <row r="468" hidden="true">
       <c r="A468" t="s" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C468" s="2"/>
       <c r="D468" t="s" s="2">
@@ -52253,10 +52248,10 @@
     </row>
     <row r="469" hidden="true">
       <c r="A469" t="s" s="2">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C469" s="2"/>
       <c r="D469" t="s" s="2">
@@ -52357,13 +52352,13 @@
     </row>
     <row r="470" hidden="true">
       <c r="A470" t="s" s="2">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D470" t="s" s="2">
         <v>73</v>
@@ -52426,7 +52421,7 @@
       </c>
       <c r="Y470" s="2"/>
       <c r="Z470" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA470" t="s" s="2">
         <v>73</v>
@@ -52461,10 +52456,10 @@
     </row>
     <row r="471" hidden="true">
       <c r="A471" t="s" s="2">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C471" s="2"/>
       <c r="D471" t="s" s="2">
@@ -52561,10 +52556,10 @@
     </row>
     <row r="472" hidden="true">
       <c r="A472" t="s" s="2">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C472" s="2"/>
       <c r="D472" t="s" s="2">
@@ -52663,10 +52658,10 @@
     </row>
     <row r="473" hidden="true">
       <c r="A473" t="s" s="2">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C473" s="2"/>
       <c r="D473" t="s" s="2">
@@ -52692,10 +52687,10 @@
         <v>128</v>
       </c>
       <c r="L473" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N473" t="s" s="2">
         <v>344</v>
@@ -52708,7 +52703,7 @@
       </c>
       <c r="Q473" s="2"/>
       <c r="R473" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="S473" t="s" s="2">
         <v>73</v>
@@ -52767,10 +52762,10 @@
     </row>
     <row r="474" hidden="true">
       <c r="A474" t="s" s="2">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C474" s="2"/>
       <c r="D474" t="s" s="2">
@@ -52869,10 +52864,10 @@
     </row>
     <row r="475" hidden="true">
       <c r="A475" t="s" s="2">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C475" s="2"/>
       <c r="D475" t="s" s="2">
@@ -52973,10 +52968,10 @@
     </row>
     <row r="476" hidden="true">
       <c r="A476" t="s" s="2">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C476" s="2"/>
       <c r="D476" t="s" s="2">
@@ -53077,10 +53072,10 @@
     </row>
     <row r="477" hidden="true">
       <c r="A477" t="s" s="2">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C477" s="2"/>
       <c r="D477" t="s" s="2">
@@ -53181,13 +53176,13 @@
     </row>
     <row r="478" hidden="true">
       <c r="A478" t="s" s="2">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D478" t="s" s="2">
         <v>73</v>
@@ -53250,7 +53245,7 @@
       </c>
       <c r="Y478" s="2"/>
       <c r="Z478" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA478" t="s" s="2">
         <v>73</v>
@@ -53285,10 +53280,10 @@
     </row>
     <row r="479" hidden="true">
       <c r="A479" t="s" s="2">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C479" s="2"/>
       <c r="D479" t="s" s="2">
@@ -53385,10 +53380,10 @@
     </row>
     <row r="480" hidden="true">
       <c r="A480" t="s" s="2">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C480" s="2"/>
       <c r="D480" t="s" s="2">
@@ -53487,10 +53482,10 @@
     </row>
     <row r="481" hidden="true">
       <c r="A481" t="s" s="2">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C481" s="2"/>
       <c r="D481" t="s" s="2">
@@ -53516,7 +53511,7 @@
         <v>128</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="M481" t="s" s="2">
         <v>343</v>
@@ -53532,7 +53527,7 @@
       </c>
       <c r="Q481" s="2"/>
       <c r="R481" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="S481" t="s" s="2">
         <v>73</v>
@@ -53591,10 +53586,10 @@
     </row>
     <row r="482" hidden="true">
       <c r="A482" t="s" s="2">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C482" s="2"/>
       <c r="D482" t="s" s="2">
@@ -53693,10 +53688,10 @@
     </row>
     <row r="483" hidden="true">
       <c r="A483" t="s" s="2">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C483" s="2"/>
       <c r="D483" t="s" s="2">
@@ -53797,10 +53792,10 @@
     </row>
     <row r="484" hidden="true">
       <c r="A484" t="s" s="2">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C484" s="2"/>
       <c r="D484" t="s" s="2">
@@ -53901,10 +53896,10 @@
     </row>
     <row r="485" hidden="true">
       <c r="A485" t="s" s="2">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C485" s="2"/>
       <c r="D485" t="s" s="2">
@@ -54005,13 +54000,13 @@
     </row>
     <row r="486" hidden="true">
       <c r="A486" t="s" s="2">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D486" t="s" s="2">
         <v>73</v>
@@ -54074,7 +54069,7 @@
       </c>
       <c r="Y486" s="2"/>
       <c r="Z486" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA486" t="s" s="2">
         <v>73</v>
@@ -54109,10 +54104,10 @@
     </row>
     <row r="487" hidden="true">
       <c r="A487" t="s" s="2">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C487" s="2"/>
       <c r="D487" t="s" s="2">
@@ -54209,10 +54204,10 @@
     </row>
     <row r="488" hidden="true">
       <c r="A488" t="s" s="2">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C488" s="2"/>
       <c r="D488" t="s" s="2">
@@ -54311,10 +54306,10 @@
     </row>
     <row r="489" hidden="true">
       <c r="A489" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C489" s="2"/>
       <c r="D489" t="s" s="2">
@@ -54340,7 +54335,7 @@
         <v>128</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M489" t="s" s="2">
         <v>343</v>
@@ -54356,7 +54351,7 @@
       </c>
       <c r="Q489" s="2"/>
       <c r="R489" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="S489" t="s" s="2">
         <v>73</v>
@@ -54415,10 +54410,10 @@
     </row>
     <row r="490" hidden="true">
       <c r="A490" t="s" s="2">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C490" s="2"/>
       <c r="D490" t="s" s="2">
@@ -54517,10 +54512,10 @@
     </row>
     <row r="491" hidden="true">
       <c r="A491" t="s" s="2">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C491" s="2"/>
       <c r="D491" t="s" s="2">
@@ -54621,10 +54616,10 @@
     </row>
     <row r="492" hidden="true">
       <c r="A492" t="s" s="2">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C492" s="2"/>
       <c r="D492" t="s" s="2">
@@ -54725,10 +54720,10 @@
     </row>
     <row r="493" hidden="true">
       <c r="A493" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C493" s="2"/>
       <c r="D493" t="s" s="2">
@@ -54829,13 +54824,13 @@
     </row>
     <row r="494" hidden="true">
       <c r="A494" t="s" s="2">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D494" t="s" s="2">
         <v>73</v>
@@ -54898,7 +54893,7 @@
       </c>
       <c r="Y494" s="2"/>
       <c r="Z494" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA494" t="s" s="2">
         <v>73</v>
@@ -54933,10 +54928,10 @@
     </row>
     <row r="495" hidden="true">
       <c r="A495" t="s" s="2">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C495" s="2"/>
       <c r="D495" t="s" s="2">
@@ -55033,10 +55028,10 @@
     </row>
     <row r="496" hidden="true">
       <c r="A496" t="s" s="2">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C496" s="2"/>
       <c r="D496" t="s" s="2">
@@ -55135,10 +55130,10 @@
     </row>
     <row r="497" hidden="true">
       <c r="A497" t="s" s="2">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C497" s="2"/>
       <c r="D497" t="s" s="2">
@@ -55164,7 +55159,7 @@
         <v>128</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="M497" t="s" s="2">
         <v>343</v>
@@ -55180,7 +55175,7 @@
       </c>
       <c r="Q497" s="2"/>
       <c r="R497" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="S497" t="s" s="2">
         <v>73</v>
@@ -55239,10 +55234,10 @@
     </row>
     <row r="498" hidden="true">
       <c r="A498" t="s" s="2">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C498" s="2"/>
       <c r="D498" t="s" s="2">
@@ -55341,10 +55336,10 @@
     </row>
     <row r="499" hidden="true">
       <c r="A499" t="s" s="2">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C499" s="2"/>
       <c r="D499" t="s" s="2">
@@ -55445,10 +55440,10 @@
     </row>
     <row r="500" hidden="true">
       <c r="A500" t="s" s="2">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C500" s="2"/>
       <c r="D500" t="s" s="2">
@@ -55549,10 +55544,10 @@
     </row>
     <row r="501" hidden="true">
       <c r="A501" t="s" s="2">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C501" s="2"/>
       <c r="D501" t="s" s="2">
@@ -55653,13 +55648,13 @@
     </row>
     <row r="502" hidden="true">
       <c r="A502" t="s" s="2">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D502" t="s" s="2">
         <v>73</v>
@@ -55722,7 +55717,7 @@
       </c>
       <c r="Y502" s="2"/>
       <c r="Z502" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA502" t="s" s="2">
         <v>73</v>
@@ -55757,10 +55752,10 @@
     </row>
     <row r="503" hidden="true">
       <c r="A503" t="s" s="2">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C503" s="2"/>
       <c r="D503" t="s" s="2">
@@ -55857,10 +55852,10 @@
     </row>
     <row r="504" hidden="true">
       <c r="A504" t="s" s="2">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C504" s="2"/>
       <c r="D504" t="s" s="2">
@@ -55959,10 +55954,10 @@
     </row>
     <row r="505" hidden="true">
       <c r="A505" t="s" s="2">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C505" s="2"/>
       <c r="D505" t="s" s="2">
@@ -55988,7 +55983,7 @@
         <v>128</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M505" t="s" s="2">
         <v>343</v>
@@ -56004,7 +55999,7 @@
       </c>
       <c r="Q505" s="2"/>
       <c r="R505" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="S505" t="s" s="2">
         <v>73</v>
@@ -56063,10 +56058,10 @@
     </row>
     <row r="506" hidden="true">
       <c r="A506" t="s" s="2">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C506" s="2"/>
       <c r="D506" t="s" s="2">
@@ -56165,10 +56160,10 @@
     </row>
     <row r="507" hidden="true">
       <c r="A507" t="s" s="2">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C507" s="2"/>
       <c r="D507" t="s" s="2">
@@ -56269,10 +56264,10 @@
     </row>
     <row r="508" hidden="true">
       <c r="A508" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C508" s="2"/>
       <c r="D508" t="s" s="2">
@@ -56373,10 +56368,10 @@
     </row>
     <row r="509" hidden="true">
       <c r="A509" t="s" s="2">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C509" s="2"/>
       <c r="D509" t="s" s="2">
@@ -56477,13 +56472,13 @@
     </row>
     <row r="510" hidden="true">
       <c r="A510" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D510" t="s" s="2">
         <v>73</v>
@@ -56546,7 +56541,7 @@
       </c>
       <c r="Y510" s="2"/>
       <c r="Z510" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA510" t="s" s="2">
         <v>73</v>
@@ -56581,10 +56576,10 @@
     </row>
     <row r="511" hidden="true">
       <c r="A511" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C511" s="2"/>
       <c r="D511" t="s" s="2">
@@ -56681,10 +56676,10 @@
     </row>
     <row r="512" hidden="true">
       <c r="A512" t="s" s="2">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C512" s="2"/>
       <c r="D512" t="s" s="2">
@@ -56783,10 +56778,10 @@
     </row>
     <row r="513" hidden="true">
       <c r="A513" t="s" s="2">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C513" s="2"/>
       <c r="D513" t="s" s="2">
@@ -56812,10 +56807,10 @@
         <v>128</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="N513" t="s" s="2">
         <v>344</v>
@@ -56828,7 +56823,7 @@
       </c>
       <c r="Q513" s="2"/>
       <c r="R513" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="S513" t="s" s="2">
         <v>73</v>
@@ -56887,10 +56882,10 @@
     </row>
     <row r="514" hidden="true">
       <c r="A514" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C514" s="2"/>
       <c r="D514" t="s" s="2">
@@ -56989,10 +56984,10 @@
     </row>
     <row r="515" hidden="true">
       <c r="A515" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C515" s="2"/>
       <c r="D515" t="s" s="2">
@@ -57093,10 +57088,10 @@
     </row>
     <row r="516" hidden="true">
       <c r="A516" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C516" s="2"/>
       <c r="D516" t="s" s="2">
@@ -57197,10 +57192,10 @@
     </row>
     <row r="517" hidden="true">
       <c r="A517" t="s" s="2">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C517" s="2"/>
       <c r="D517" t="s" s="2">
@@ -57301,13 +57296,13 @@
     </row>
     <row r="518" hidden="true">
       <c r="A518" t="s" s="2">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D518" t="s" s="2">
         <v>73</v>
@@ -57370,7 +57365,7 @@
       </c>
       <c r="Y518" s="2"/>
       <c r="Z518" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA518" t="s" s="2">
         <v>73</v>
@@ -57405,10 +57400,10 @@
     </row>
     <row r="519" hidden="true">
       <c r="A519" t="s" s="2">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C519" s="2"/>
       <c r="D519" t="s" s="2">
@@ -57505,10 +57500,10 @@
     </row>
     <row r="520" hidden="true">
       <c r="A520" t="s" s="2">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C520" s="2"/>
       <c r="D520" t="s" s="2">
@@ -57607,10 +57602,10 @@
     </row>
     <row r="521" hidden="true">
       <c r="A521" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C521" s="2"/>
       <c r="D521" t="s" s="2">
@@ -57636,10 +57631,10 @@
         <v>128</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="N521" t="s" s="2">
         <v>344</v>
@@ -57652,7 +57647,7 @@
       </c>
       <c r="Q521" s="2"/>
       <c r="R521" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="S521" t="s" s="2">
         <v>73</v>
@@ -57711,10 +57706,10 @@
     </row>
     <row r="522" hidden="true">
       <c r="A522" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C522" s="2"/>
       <c r="D522" t="s" s="2">
@@ -57813,10 +57808,10 @@
     </row>
     <row r="523" hidden="true">
       <c r="A523" t="s" s="2">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C523" s="2"/>
       <c r="D523" t="s" s="2">
@@ -57917,10 +57912,10 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C524" s="2"/>
       <c r="D524" t="s" s="2">
@@ -58021,10 +58016,10 @@
     </row>
     <row r="525" hidden="true">
       <c r="A525" t="s" s="2">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C525" s="2"/>
       <c r="D525" t="s" s="2">
@@ -58125,13 +58120,13 @@
     </row>
     <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D526" t="s" s="2">
         <v>73</v>
@@ -58194,7 +58189,7 @@
       </c>
       <c r="Y526" s="2"/>
       <c r="Z526" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA526" t="s" s="2">
         <v>73</v>
@@ -58229,10 +58224,10 @@
     </row>
     <row r="527" hidden="true">
       <c r="A527" t="s" s="2">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C527" s="2"/>
       <c r="D527" t="s" s="2">
@@ -58329,10 +58324,10 @@
     </row>
     <row r="528" hidden="true">
       <c r="A528" t="s" s="2">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C528" s="2"/>
       <c r="D528" t="s" s="2">
@@ -58431,10 +58426,10 @@
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C529" s="2"/>
       <c r="D529" t="s" s="2">
@@ -58460,7 +58455,7 @@
         <v>128</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M529" t="s" s="2">
         <v>343</v>
@@ -58476,7 +58471,7 @@
       </c>
       <c r="Q529" s="2"/>
       <c r="R529" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S529" t="s" s="2">
         <v>73</v>
@@ -58535,10 +58530,10 @@
     </row>
     <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C530" s="2"/>
       <c r="D530" t="s" s="2">
@@ -58637,10 +58632,10 @@
     </row>
     <row r="531" hidden="true">
       <c r="A531" t="s" s="2">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C531" s="2"/>
       <c r="D531" t="s" s="2">
@@ -58741,10 +58736,10 @@
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C532" s="2"/>
       <c r="D532" t="s" s="2">
@@ -58845,10 +58840,10 @@
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C533" s="2"/>
       <c r="D533" t="s" s="2">
@@ -58949,13 +58944,13 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D534" t="s" s="2">
         <v>73</v>
@@ -59018,7 +59013,7 @@
       </c>
       <c r="Y534" s="2"/>
       <c r="Z534" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA534" t="s" s="2">
         <v>73</v>
@@ -59053,10 +59048,10 @@
     </row>
     <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C535" s="2"/>
       <c r="D535" t="s" s="2">
@@ -59153,10 +59148,10 @@
     </row>
     <row r="536" hidden="true">
       <c r="A536" t="s" s="2">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C536" s="2"/>
       <c r="D536" t="s" s="2">
@@ -59255,10 +59250,10 @@
     </row>
     <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C537" s="2"/>
       <c r="D537" t="s" s="2">
@@ -59284,10 +59279,10 @@
         <v>128</v>
       </c>
       <c r="L537" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="N537" t="s" s="2">
         <v>344</v>
@@ -59300,7 +59295,7 @@
       </c>
       <c r="Q537" s="2"/>
       <c r="R537" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="S537" t="s" s="2">
         <v>73</v>
@@ -59359,10 +59354,10 @@
     </row>
     <row r="538" hidden="true">
       <c r="A538" t="s" s="2">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C538" s="2"/>
       <c r="D538" t="s" s="2">
@@ -59461,10 +59456,10 @@
     </row>
     <row r="539" hidden="true">
       <c r="A539" t="s" s="2">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C539" s="2"/>
       <c r="D539" t="s" s="2">
@@ -59565,10 +59560,10 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C540" s="2"/>
       <c r="D540" t="s" s="2">
@@ -59669,10 +59664,10 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C541" s="2"/>
       <c r="D541" t="s" s="2">
@@ -59773,13 +59768,13 @@
     </row>
     <row r="542" hidden="true">
       <c r="A542" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D542" t="s" s="2">
         <v>73</v>
@@ -59842,7 +59837,7 @@
       </c>
       <c r="Y542" s="2"/>
       <c r="Z542" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA542" t="s" s="2">
         <v>73</v>
@@ -59877,10 +59872,10 @@
     </row>
     <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C543" s="2"/>
       <c r="D543" t="s" s="2">
@@ -59977,10 +59972,10 @@
     </row>
     <row r="544" hidden="true">
       <c r="A544" t="s" s="2">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C544" s="2"/>
       <c r="D544" t="s" s="2">
@@ -60079,10 +60074,10 @@
     </row>
     <row r="545" hidden="true">
       <c r="A545" t="s" s="2">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C545" s="2"/>
       <c r="D545" t="s" s="2">
@@ -60108,10 +60103,10 @@
         <v>128</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N545" t="s" s="2">
         <v>344</v>
@@ -60124,7 +60119,7 @@
       </c>
       <c r="Q545" s="2"/>
       <c r="R545" t="s" s="2">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="S545" t="s" s="2">
         <v>73</v>
@@ -60183,10 +60178,10 @@
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C546" s="2"/>
       <c r="D546" t="s" s="2">
@@ -60285,10 +60280,10 @@
     </row>
     <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C547" s="2"/>
       <c r="D547" t="s" s="2">
@@ -60389,10 +60384,10 @@
     </row>
     <row r="548" hidden="true">
       <c r="A548" t="s" s="2">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C548" s="2"/>
       <c r="D548" t="s" s="2">
@@ -60493,10 +60488,10 @@
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C549" s="2"/>
       <c r="D549" t="s" s="2">
@@ -60597,13 +60592,13 @@
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D550" t="s" s="2">
         <v>73</v>
@@ -60666,7 +60661,7 @@
       </c>
       <c r="Y550" s="2"/>
       <c r="Z550" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA550" t="s" s="2">
         <v>73</v>
@@ -60701,10 +60696,10 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C551" s="2"/>
       <c r="D551" t="s" s="2">
@@ -60801,10 +60796,10 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C552" s="2"/>
       <c r="D552" t="s" s="2">
@@ -60903,10 +60898,10 @@
     </row>
     <row r="553" hidden="true">
       <c r="A553" t="s" s="2">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C553" s="2"/>
       <c r="D553" t="s" s="2">
@@ -60932,7 +60927,7 @@
         <v>128</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="M553" t="s" s="2">
         <v>343</v>
@@ -60948,7 +60943,7 @@
       </c>
       <c r="Q553" s="2"/>
       <c r="R553" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="S553" t="s" s="2">
         <v>73</v>
@@ -61007,10 +61002,10 @@
     </row>
     <row r="554" hidden="true">
       <c r="A554" t="s" s="2">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C554" s="2"/>
       <c r="D554" t="s" s="2">
@@ -61109,10 +61104,10 @@
     </row>
     <row r="555" hidden="true">
       <c r="A555" t="s" s="2">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C555" s="2"/>
       <c r="D555" t="s" s="2">
@@ -61213,10 +61208,10 @@
     </row>
     <row r="556" hidden="true">
       <c r="A556" t="s" s="2">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C556" s="2"/>
       <c r="D556" t="s" s="2">
@@ -61317,10 +61312,10 @@
     </row>
     <row r="557" hidden="true">
       <c r="A557" t="s" s="2">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C557" s="2"/>
       <c r="D557" t="s" s="2">
@@ -61421,13 +61416,13 @@
     </row>
     <row r="558" hidden="true">
       <c r="A558" t="s" s="2">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="D558" t="s" s="2">
         <v>73</v>
@@ -61452,7 +61447,7 @@
         <v>140</v>
       </c>
       <c r="L558" t="s" s="2">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="M558" t="s" s="2">
         <v>335</v>
@@ -61490,7 +61485,7 @@
       </c>
       <c r="Y558" s="2"/>
       <c r="Z558" t="s" s="2">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="AA558" t="s" s="2">
         <v>73</v>
@@ -61525,13 +61520,13 @@
     </row>
     <row r="559" hidden="true">
       <c r="A559" t="s" s="2">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D559" t="s" s="2">
         <v>73</v>
@@ -61556,7 +61551,7 @@
         <v>140</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="M559" t="s" s="2">
         <v>335</v>
@@ -61594,7 +61589,7 @@
       </c>
       <c r="Y559" s="2"/>
       <c r="Z559" t="s" s="2">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="AA559" t="s" s="2">
         <v>73</v>
@@ -61629,10 +61624,10 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C560" s="2"/>
       <c r="D560" t="s" s="2">
@@ -61733,10 +61728,10 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C561" s="2"/>
       <c r="D561" t="s" s="2">
@@ -61762,16 +61757,16 @@
         <v>252</v>
       </c>
       <c r="L561" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N561" t="s" s="2">
         <v>393</v>
       </c>
       <c r="O561" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="P561" t="s" s="2">
         <v>73</v>
@@ -61820,7 +61815,7 @@
         <v>73</v>
       </c>
       <c r="AF561" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AG561" t="s" s="2">
         <v>74</v>
@@ -61837,10 +61832,10 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C562" s="2"/>
       <c r="D562" t="s" s="2">
@@ -61937,10 +61932,10 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C563" s="2"/>
       <c r="D563" t="s" s="2">
@@ -62039,10 +62034,10 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C564" s="2"/>
       <c r="D564" t="s" s="2">
@@ -62068,7 +62063,7 @@
         <v>259</v>
       </c>
       <c r="L564" t="s" s="2">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="M564" t="s" s="2">
         <v>261</v>
@@ -62141,10 +62136,10 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C565" s="2"/>
       <c r="D565" t="s" s="2">
@@ -62170,7 +62165,7 @@
         <v>259</v>
       </c>
       <c r="L565" t="s" s="2">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="M565" t="s" s="2">
         <v>268</v>
@@ -62245,10 +62240,10 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C566" s="2"/>
       <c r="D566" t="s" s="2">
@@ -62274,13 +62269,13 @@
         <v>397</v>
       </c>
       <c r="L566" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M566" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="N566" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="M566" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="N566" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="O566" s="2"/>
       <c r="P566" t="s" s="2">
@@ -62330,7 +62325,7 @@
         <v>73</v>
       </c>
       <c r="AF566" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AG566" t="s" s="2">
         <v>74</v>
@@ -62347,13 +62342,13 @@
     </row>
     <row r="567" hidden="true">
       <c r="A567" t="s" s="2">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D567" t="s" s="2">
         <v>73</v>
@@ -62375,13 +62370,13 @@
         <v>73</v>
       </c>
       <c r="K567" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L567" t="s" s="2">
+        <v>1113</v>
+      </c>
+      <c r="M567" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="L567" t="s" s="2">
-        <v>1115</v>
-      </c>
-      <c r="M567" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N567" s="2"/>
       <c r="O567" s="2"/>
@@ -62432,7 +62427,7 @@
         <v>73</v>
       </c>
       <c r="AF567" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG567" t="s" s="2">
         <v>74</v>
@@ -62449,10 +62444,10 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C568" s="2"/>
       <c r="D568" t="s" s="2">
@@ -62549,10 +62544,10 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C569" s="2"/>
       <c r="D569" t="s" s="2">
@@ -62651,14 +62646,14 @@
     </row>
     <row r="570" hidden="true">
       <c r="A570" t="s" s="2">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C570" s="2"/>
       <c r="D570" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E570" s="2"/>
       <c r="F570" t="s" s="2">
@@ -62680,10 +62675,10 @@
         <v>102</v>
       </c>
       <c r="L570" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="M570" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N570" t="s" s="2">
         <v>105</v>
@@ -62738,7 +62733,7 @@
         <v>73</v>
       </c>
       <c r="AF570" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AG570" t="s" s="2">
         <v>74</v>
@@ -62755,10 +62750,10 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C571" s="2"/>
       <c r="D571" t="s" s="2">
@@ -62784,14 +62779,14 @@
         <v>305</v>
       </c>
       <c r="L571" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="M571" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="N571" s="2"/>
       <c r="O571" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P571" t="s" s="2">
         <v>73</v>
@@ -62840,7 +62835,7 @@
         <v>73</v>
       </c>
       <c r="AF571" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AG571" t="s" s="2">
         <v>74</v>
@@ -62857,10 +62852,10 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C572" s="2"/>
       <c r="D572" t="s" s="2">
@@ -62886,13 +62881,13 @@
         <v>323</v>
       </c>
       <c r="L572" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M572" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N572" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M572" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N572" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O572" s="2"/>
       <c r="P572" t="s" s="2">
@@ -62921,10 +62916,10 @@
         <v>152</v>
       </c>
       <c r="Y572" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="Z572" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AA572" t="s" s="2">
         <v>73</v>
@@ -62942,7 +62937,7 @@
         <v>73</v>
       </c>
       <c r="AF572" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AG572" t="s" s="2">
         <v>81</v>
@@ -62959,10 +62954,10 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C573" s="2"/>
       <c r="D573" t="s" s="2">
@@ -63059,10 +63054,10 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C574" s="2"/>
       <c r="D574" t="s" s="2">
@@ -63161,10 +63156,10 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C575" s="2"/>
       <c r="D575" t="s" s="2">
@@ -63236,7 +63231,7 @@
         <v>73</v>
       </c>
       <c r="AB575" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AC575" s="2"/>
       <c r="AD575" t="s" s="2">
@@ -63263,13 +63258,13 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D576" t="s" s="2">
         <v>73</v>
@@ -63332,7 +63327,7 @@
       </c>
       <c r="Y576" s="2"/>
       <c r="Z576" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA576" t="s" s="2">
         <v>73</v>
@@ -63367,10 +63362,10 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C577" s="2"/>
       <c r="D577" t="s" s="2">
@@ -63467,10 +63462,10 @@
     </row>
     <row r="578" hidden="true">
       <c r="A578" t="s" s="2">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C578" s="2"/>
       <c r="D578" t="s" s="2">
@@ -63569,10 +63564,10 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C579" s="2"/>
       <c r="D579" t="s" s="2">
@@ -63598,7 +63593,7 @@
         <v>128</v>
       </c>
       <c r="L579" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="M579" t="s" s="2">
         <v>343</v>
@@ -63614,7 +63609,7 @@
       </c>
       <c r="Q579" s="2"/>
       <c r="R579" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S579" t="s" s="2">
         <v>73</v>
@@ -63673,10 +63668,10 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C580" s="2"/>
       <c r="D580" t="s" s="2">
@@ -63775,10 +63770,10 @@
     </row>
     <row r="581" hidden="true">
       <c r="A581" t="s" s="2">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C581" s="2"/>
       <c r="D581" t="s" s="2">
@@ -63879,10 +63874,10 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C582" s="2"/>
       <c r="D582" t="s" s="2">
@@ -63983,10 +63978,10 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C583" s="2"/>
       <c r="D583" t="s" s="2">
@@ -64087,13 +64082,13 @@
     </row>
     <row r="584" hidden="true">
       <c r="A584" t="s" s="2">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D584" t="s" s="2">
         <v>73</v>
@@ -64156,7 +64151,7 @@
       </c>
       <c r="Y584" s="2"/>
       <c r="Z584" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA584" t="s" s="2">
         <v>73</v>
@@ -64191,10 +64186,10 @@
     </row>
     <row r="585" hidden="true">
       <c r="A585" t="s" s="2">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C585" s="2"/>
       <c r="D585" t="s" s="2">
@@ -64291,10 +64286,10 @@
     </row>
     <row r="586" hidden="true">
       <c r="A586" t="s" s="2">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C586" s="2"/>
       <c r="D586" t="s" s="2">
@@ -64393,10 +64388,10 @@
     </row>
     <row r="587" hidden="true">
       <c r="A587" t="s" s="2">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C587" s="2"/>
       <c r="D587" t="s" s="2">
@@ -64422,7 +64417,7 @@
         <v>128</v>
       </c>
       <c r="L587" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="M587" t="s" s="2">
         <v>343</v>
@@ -64438,7 +64433,7 @@
       </c>
       <c r="Q587" s="2"/>
       <c r="R587" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S587" t="s" s="2">
         <v>73</v>
@@ -64497,10 +64492,10 @@
     </row>
     <row r="588" hidden="true">
       <c r="A588" t="s" s="2">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C588" s="2"/>
       <c r="D588" t="s" s="2">
@@ -64599,10 +64594,10 @@
     </row>
     <row r="589" hidden="true">
       <c r="A589" t="s" s="2">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C589" s="2"/>
       <c r="D589" t="s" s="2">
@@ -64703,10 +64698,10 @@
     </row>
     <row r="590" hidden="true">
       <c r="A590" t="s" s="2">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C590" s="2"/>
       <c r="D590" t="s" s="2">
@@ -64807,10 +64802,10 @@
     </row>
     <row r="591" hidden="true">
       <c r="A591" t="s" s="2">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C591" s="2"/>
       <c r="D591" t="s" s="2">
@@ -64911,13 +64906,13 @@
     </row>
     <row r="592" hidden="true">
       <c r="A592" t="s" s="2">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D592" t="s" s="2">
         <v>73</v>
@@ -64980,7 +64975,7 @@
       </c>
       <c r="Y592" s="2"/>
       <c r="Z592" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA592" t="s" s="2">
         <v>73</v>
@@ -65015,10 +65010,10 @@
     </row>
     <row r="593" hidden="true">
       <c r="A593" t="s" s="2">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C593" s="2"/>
       <c r="D593" t="s" s="2">
@@ -65115,10 +65110,10 @@
     </row>
     <row r="594" hidden="true">
       <c r="A594" t="s" s="2">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C594" s="2"/>
       <c r="D594" t="s" s="2">
@@ -65217,10 +65212,10 @@
     </row>
     <row r="595" hidden="true">
       <c r="A595" t="s" s="2">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C595" s="2"/>
       <c r="D595" t="s" s="2">
@@ -65246,7 +65241,7 @@
         <v>128</v>
       </c>
       <c r="L595" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="M595" t="s" s="2">
         <v>343</v>
@@ -65262,7 +65257,7 @@
       </c>
       <c r="Q595" s="2"/>
       <c r="R595" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S595" t="s" s="2">
         <v>73</v>
@@ -65321,10 +65316,10 @@
     </row>
     <row r="596" hidden="true">
       <c r="A596" t="s" s="2">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C596" s="2"/>
       <c r="D596" t="s" s="2">
@@ -65423,10 +65418,10 @@
     </row>
     <row r="597" hidden="true">
       <c r="A597" t="s" s="2">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C597" s="2"/>
       <c r="D597" t="s" s="2">
@@ -65527,10 +65522,10 @@
     </row>
     <row r="598" hidden="true">
       <c r="A598" t="s" s="2">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C598" s="2"/>
       <c r="D598" t="s" s="2">
@@ -65631,10 +65626,10 @@
     </row>
     <row r="599" hidden="true">
       <c r="A599" t="s" s="2">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C599" s="2"/>
       <c r="D599" t="s" s="2">
@@ -65735,13 +65730,13 @@
     </row>
     <row r="600" hidden="true">
       <c r="A600" t="s" s="2">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="B600" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C600" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D600" t="s" s="2">
         <v>73</v>
@@ -65804,7 +65799,7 @@
       </c>
       <c r="Y600" s="2"/>
       <c r="Z600" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA600" t="s" s="2">
         <v>73</v>
@@ -65839,10 +65834,10 @@
     </row>
     <row r="601" hidden="true">
       <c r="A601" t="s" s="2">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C601" s="2"/>
       <c r="D601" t="s" s="2">
@@ -65939,10 +65934,10 @@
     </row>
     <row r="602" hidden="true">
       <c r="A602" t="s" s="2">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B602" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C602" s="2"/>
       <c r="D602" t="s" s="2">
@@ -66041,10 +66036,10 @@
     </row>
     <row r="603" hidden="true">
       <c r="A603" t="s" s="2">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B603" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C603" s="2"/>
       <c r="D603" t="s" s="2">
@@ -66070,10 +66065,10 @@
         <v>128</v>
       </c>
       <c r="L603" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="M603" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="N603" t="s" s="2">
         <v>344</v>
@@ -66086,7 +66081,7 @@
       </c>
       <c r="Q603" s="2"/>
       <c r="R603" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="S603" t="s" s="2">
         <v>73</v>
@@ -66145,10 +66140,10 @@
     </row>
     <row r="604" hidden="true">
       <c r="A604" t="s" s="2">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B604" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C604" s="2"/>
       <c r="D604" t="s" s="2">
@@ -66247,10 +66242,10 @@
     </row>
     <row r="605" hidden="true">
       <c r="A605" t="s" s="2">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B605" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C605" s="2"/>
       <c r="D605" t="s" s="2">
@@ -66351,10 +66346,10 @@
     </row>
     <row r="606" hidden="true">
       <c r="A606" t="s" s="2">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B606" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C606" s="2"/>
       <c r="D606" t="s" s="2">
@@ -66455,10 +66450,10 @@
     </row>
     <row r="607" hidden="true">
       <c r="A607" t="s" s="2">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B607" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C607" s="2"/>
       <c r="D607" t="s" s="2">
@@ -66559,13 +66554,13 @@
     </row>
     <row r="608" hidden="true">
       <c r="A608" t="s" s="2">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B608" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C608" t="s" s="2">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D608" t="s" s="2">
         <v>73</v>
@@ -66628,7 +66623,7 @@
       </c>
       <c r="Y608" s="2"/>
       <c r="Z608" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA608" t="s" s="2">
         <v>73</v>
@@ -66663,10 +66658,10 @@
     </row>
     <row r="609" hidden="true">
       <c r="A609" t="s" s="2">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B609" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C609" s="2"/>
       <c r="D609" t="s" s="2">
@@ -66763,10 +66758,10 @@
     </row>
     <row r="610" hidden="true">
       <c r="A610" t="s" s="2">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B610" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C610" s="2"/>
       <c r="D610" t="s" s="2">
@@ -66865,10 +66860,10 @@
     </row>
     <row r="611" hidden="true">
       <c r="A611" t="s" s="2">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B611" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C611" s="2"/>
       <c r="D611" t="s" s="2">
@@ -66894,7 +66889,7 @@
         <v>128</v>
       </c>
       <c r="L611" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="M611" t="s" s="2">
         <v>343</v>
@@ -66910,7 +66905,7 @@
       </c>
       <c r="Q611" s="2"/>
       <c r="R611" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="S611" t="s" s="2">
         <v>73</v>
@@ -66969,10 +66964,10 @@
     </row>
     <row r="612" hidden="true">
       <c r="A612" t="s" s="2">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B612" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C612" s="2"/>
       <c r="D612" t="s" s="2">
@@ -67071,10 +67066,10 @@
     </row>
     <row r="613" hidden="true">
       <c r="A613" t="s" s="2">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B613" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C613" s="2"/>
       <c r="D613" t="s" s="2">
@@ -67175,10 +67170,10 @@
     </row>
     <row r="614" hidden="true">
       <c r="A614" t="s" s="2">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B614" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C614" s="2"/>
       <c r="D614" t="s" s="2">
@@ -67279,10 +67274,10 @@
     </row>
     <row r="615" hidden="true">
       <c r="A615" t="s" s="2">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B615" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C615" s="2"/>
       <c r="D615" t="s" s="2">
@@ -67383,13 +67378,13 @@
     </row>
     <row r="616" hidden="true">
       <c r="A616" t="s" s="2">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B616" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C616" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D616" t="s" s="2">
         <v>73</v>
@@ -67452,7 +67447,7 @@
       </c>
       <c r="Y616" s="2"/>
       <c r="Z616" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA616" t="s" s="2">
         <v>73</v>
@@ -67487,10 +67482,10 @@
     </row>
     <row r="617" hidden="true">
       <c r="A617" t="s" s="2">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B617" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C617" s="2"/>
       <c r="D617" t="s" s="2">
@@ -67587,10 +67582,10 @@
     </row>
     <row r="618" hidden="true">
       <c r="A618" t="s" s="2">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="B618" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C618" s="2"/>
       <c r="D618" t="s" s="2">
@@ -67689,10 +67684,10 @@
     </row>
     <row r="619" hidden="true">
       <c r="A619" t="s" s="2">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="B619" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C619" s="2"/>
       <c r="D619" t="s" s="2">
@@ -67718,7 +67713,7 @@
         <v>128</v>
       </c>
       <c r="L619" t="s" s="2">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="M619" t="s" s="2">
         <v>343</v>
@@ -67734,7 +67729,7 @@
       </c>
       <c r="Q619" s="2"/>
       <c r="R619" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="S619" t="s" s="2">
         <v>73</v>
@@ -67793,10 +67788,10 @@
     </row>
     <row r="620" hidden="true">
       <c r="A620" t="s" s="2">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B620" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C620" s="2"/>
       <c r="D620" t="s" s="2">
@@ -67895,10 +67890,10 @@
     </row>
     <row r="621" hidden="true">
       <c r="A621" t="s" s="2">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B621" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C621" s="2"/>
       <c r="D621" t="s" s="2">
@@ -67999,10 +67994,10 @@
     </row>
     <row r="622" hidden="true">
       <c r="A622" t="s" s="2">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B622" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C622" s="2"/>
       <c r="D622" t="s" s="2">
@@ -68103,10 +68098,10 @@
     </row>
     <row r="623" hidden="true">
       <c r="A623" t="s" s="2">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B623" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C623" s="2"/>
       <c r="D623" t="s" s="2">
@@ -68207,13 +68202,13 @@
     </row>
     <row r="624" hidden="true">
       <c r="A624" t="s" s="2">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B624" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C624" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D624" t="s" s="2">
         <v>73</v>
@@ -68276,7 +68271,7 @@
       </c>
       <c r="Y624" s="2"/>
       <c r="Z624" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA624" t="s" s="2">
         <v>73</v>
@@ -68311,10 +68306,10 @@
     </row>
     <row r="625" hidden="true">
       <c r="A625" t="s" s="2">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B625" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C625" s="2"/>
       <c r="D625" t="s" s="2">
@@ -68411,10 +68406,10 @@
     </row>
     <row r="626" hidden="true">
       <c r="A626" t="s" s="2">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B626" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C626" s="2"/>
       <c r="D626" t="s" s="2">
@@ -68513,10 +68508,10 @@
     </row>
     <row r="627" hidden="true">
       <c r="A627" t="s" s="2">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B627" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C627" s="2"/>
       <c r="D627" t="s" s="2">
@@ -68542,7 +68537,7 @@
         <v>128</v>
       </c>
       <c r="L627" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="M627" t="s" s="2">
         <v>343</v>
@@ -68558,7 +68553,7 @@
       </c>
       <c r="Q627" s="2"/>
       <c r="R627" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="S627" t="s" s="2">
         <v>73</v>
@@ -68617,10 +68612,10 @@
     </row>
     <row r="628" hidden="true">
       <c r="A628" t="s" s="2">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B628" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C628" s="2"/>
       <c r="D628" t="s" s="2">
@@ -68719,10 +68714,10 @@
     </row>
     <row r="629" hidden="true">
       <c r="A629" t="s" s="2">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B629" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C629" s="2"/>
       <c r="D629" t="s" s="2">
@@ -68823,10 +68818,10 @@
     </row>
     <row r="630" hidden="true">
       <c r="A630" t="s" s="2">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B630" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C630" s="2"/>
       <c r="D630" t="s" s="2">
@@ -68927,10 +68922,10 @@
     </row>
     <row r="631" hidden="true">
       <c r="A631" t="s" s="2">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B631" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C631" s="2"/>
       <c r="D631" t="s" s="2">
@@ -69031,13 +69026,13 @@
     </row>
     <row r="632" hidden="true">
       <c r="A632" t="s" s="2">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B632" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C632" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D632" t="s" s="2">
         <v>73</v>
@@ -69100,7 +69095,7 @@
       </c>
       <c r="Y632" s="2"/>
       <c r="Z632" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA632" t="s" s="2">
         <v>73</v>
@@ -69135,10 +69130,10 @@
     </row>
     <row r="633" hidden="true">
       <c r="A633" t="s" s="2">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B633" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C633" s="2"/>
       <c r="D633" t="s" s="2">
@@ -69235,10 +69230,10 @@
     </row>
     <row r="634" hidden="true">
       <c r="A634" t="s" s="2">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B634" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C634" s="2"/>
       <c r="D634" t="s" s="2">
@@ -69337,10 +69332,10 @@
     </row>
     <row r="635" hidden="true">
       <c r="A635" t="s" s="2">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B635" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C635" s="2"/>
       <c r="D635" t="s" s="2">
@@ -69366,7 +69361,7 @@
         <v>128</v>
       </c>
       <c r="L635" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="M635" t="s" s="2">
         <v>343</v>
@@ -69382,7 +69377,7 @@
       </c>
       <c r="Q635" s="2"/>
       <c r="R635" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="S635" t="s" s="2">
         <v>73</v>
@@ -69441,10 +69436,10 @@
     </row>
     <row r="636" hidden="true">
       <c r="A636" t="s" s="2">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B636" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C636" s="2"/>
       <c r="D636" t="s" s="2">
@@ -69543,10 +69538,10 @@
     </row>
     <row r="637" hidden="true">
       <c r="A637" t="s" s="2">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B637" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C637" s="2"/>
       <c r="D637" t="s" s="2">
@@ -69647,10 +69642,10 @@
     </row>
     <row r="638" hidden="true">
       <c r="A638" t="s" s="2">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B638" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C638" s="2"/>
       <c r="D638" t="s" s="2">
@@ -69751,10 +69746,10 @@
     </row>
     <row r="639" hidden="true">
       <c r="A639" t="s" s="2">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B639" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C639" s="2"/>
       <c r="D639" t="s" s="2">
@@ -69855,13 +69850,13 @@
     </row>
     <row r="640" hidden="true">
       <c r="A640" t="s" s="2">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B640" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C640" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D640" t="s" s="2">
         <v>73</v>
@@ -69924,7 +69919,7 @@
       </c>
       <c r="Y640" s="2"/>
       <c r="Z640" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA640" t="s" s="2">
         <v>73</v>
@@ -69959,10 +69954,10 @@
     </row>
     <row r="641" hidden="true">
       <c r="A641" t="s" s="2">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B641" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C641" s="2"/>
       <c r="D641" t="s" s="2">
@@ -70059,10 +70054,10 @@
     </row>
     <row r="642" hidden="true">
       <c r="A642" t="s" s="2">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B642" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C642" s="2"/>
       <c r="D642" t="s" s="2">
@@ -70161,10 +70156,10 @@
     </row>
     <row r="643" hidden="true">
       <c r="A643" t="s" s="2">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B643" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C643" s="2"/>
       <c r="D643" t="s" s="2">
@@ -70190,10 +70185,10 @@
         <v>128</v>
       </c>
       <c r="L643" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="M643" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="N643" t="s" s="2">
         <v>344</v>
@@ -70206,7 +70201,7 @@
       </c>
       <c r="Q643" s="2"/>
       <c r="R643" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="S643" t="s" s="2">
         <v>73</v>
@@ -70265,10 +70260,10 @@
     </row>
     <row r="644" hidden="true">
       <c r="A644" t="s" s="2">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B644" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C644" s="2"/>
       <c r="D644" t="s" s="2">
@@ -70367,10 +70362,10 @@
     </row>
     <row r="645" hidden="true">
       <c r="A645" t="s" s="2">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B645" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C645" s="2"/>
       <c r="D645" t="s" s="2">
@@ -70471,10 +70466,10 @@
     </row>
     <row r="646" hidden="true">
       <c r="A646" t="s" s="2">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B646" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C646" s="2"/>
       <c r="D646" t="s" s="2">
@@ -70575,10 +70570,10 @@
     </row>
     <row r="647" hidden="true">
       <c r="A647" t="s" s="2">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B647" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C647" s="2"/>
       <c r="D647" t="s" s="2">
@@ -70679,13 +70674,13 @@
     </row>
     <row r="648" hidden="true">
       <c r="A648" t="s" s="2">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B648" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C648" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D648" t="s" s="2">
         <v>73</v>
@@ -70748,7 +70743,7 @@
       </c>
       <c r="Y648" s="2"/>
       <c r="Z648" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA648" t="s" s="2">
         <v>73</v>
@@ -70783,10 +70778,10 @@
     </row>
     <row r="649" hidden="true">
       <c r="A649" t="s" s="2">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B649" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C649" s="2"/>
       <c r="D649" t="s" s="2">
@@ -70883,10 +70878,10 @@
     </row>
     <row r="650" hidden="true">
       <c r="A650" t="s" s="2">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B650" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C650" s="2"/>
       <c r="D650" t="s" s="2">
@@ -70985,10 +70980,10 @@
     </row>
     <row r="651" hidden="true">
       <c r="A651" t="s" s="2">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B651" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C651" s="2"/>
       <c r="D651" t="s" s="2">
@@ -71014,10 +71009,10 @@
         <v>128</v>
       </c>
       <c r="L651" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="M651" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="N651" t="s" s="2">
         <v>344</v>
@@ -71030,7 +71025,7 @@
       </c>
       <c r="Q651" s="2"/>
       <c r="R651" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="S651" t="s" s="2">
         <v>73</v>
@@ -71089,10 +71084,10 @@
     </row>
     <row r="652" hidden="true">
       <c r="A652" t="s" s="2">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B652" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C652" s="2"/>
       <c r="D652" t="s" s="2">
@@ -71191,10 +71186,10 @@
     </row>
     <row r="653" hidden="true">
       <c r="A653" t="s" s="2">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B653" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C653" s="2"/>
       <c r="D653" t="s" s="2">
@@ -71295,10 +71290,10 @@
     </row>
     <row r="654" hidden="true">
       <c r="A654" t="s" s="2">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B654" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C654" s="2"/>
       <c r="D654" t="s" s="2">
@@ -71399,10 +71394,10 @@
     </row>
     <row r="655" hidden="true">
       <c r="A655" t="s" s="2">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B655" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C655" s="2"/>
       <c r="D655" t="s" s="2">
@@ -71503,13 +71498,13 @@
     </row>
     <row r="656" hidden="true">
       <c r="A656" t="s" s="2">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B656" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C656" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D656" t="s" s="2">
         <v>73</v>
@@ -71572,7 +71567,7 @@
       </c>
       <c r="Y656" s="2"/>
       <c r="Z656" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA656" t="s" s="2">
         <v>73</v>
@@ -71607,10 +71602,10 @@
     </row>
     <row r="657" hidden="true">
       <c r="A657" t="s" s="2">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B657" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C657" s="2"/>
       <c r="D657" t="s" s="2">
@@ -71707,10 +71702,10 @@
     </row>
     <row r="658" hidden="true">
       <c r="A658" t="s" s="2">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B658" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C658" s="2"/>
       <c r="D658" t="s" s="2">
@@ -71809,10 +71804,10 @@
     </row>
     <row r="659" hidden="true">
       <c r="A659" t="s" s="2">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B659" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C659" s="2"/>
       <c r="D659" t="s" s="2">
@@ -71838,7 +71833,7 @@
         <v>128</v>
       </c>
       <c r="L659" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M659" t="s" s="2">
         <v>343</v>
@@ -71854,7 +71849,7 @@
       </c>
       <c r="Q659" s="2"/>
       <c r="R659" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S659" t="s" s="2">
         <v>73</v>
@@ -71913,10 +71908,10 @@
     </row>
     <row r="660" hidden="true">
       <c r="A660" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B660" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C660" s="2"/>
       <c r="D660" t="s" s="2">
@@ -72015,10 +72010,10 @@
     </row>
     <row r="661" hidden="true">
       <c r="A661" t="s" s="2">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B661" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C661" s="2"/>
       <c r="D661" t="s" s="2">
@@ -72119,10 +72114,10 @@
     </row>
     <row r="662" hidden="true">
       <c r="A662" t="s" s="2">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C662" s="2"/>
       <c r="D662" t="s" s="2">
@@ -72223,10 +72218,10 @@
     </row>
     <row r="663" hidden="true">
       <c r="A663" t="s" s="2">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B663" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C663" s="2"/>
       <c r="D663" t="s" s="2">
@@ -72327,13 +72322,13 @@
     </row>
     <row r="664" hidden="true">
       <c r="A664" t="s" s="2">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B664" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C664" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D664" t="s" s="2">
         <v>73</v>
@@ -72396,7 +72391,7 @@
       </c>
       <c r="Y664" s="2"/>
       <c r="Z664" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA664" t="s" s="2">
         <v>73</v>
@@ -72431,10 +72426,10 @@
     </row>
     <row r="665" hidden="true">
       <c r="A665" t="s" s="2">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B665" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C665" s="2"/>
       <c r="D665" t="s" s="2">
@@ -72531,10 +72526,10 @@
     </row>
     <row r="666" hidden="true">
       <c r="A666" t="s" s="2">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B666" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C666" s="2"/>
       <c r="D666" t="s" s="2">
@@ -72633,10 +72628,10 @@
     </row>
     <row r="667" hidden="true">
       <c r="A667" t="s" s="2">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C667" s="2"/>
       <c r="D667" t="s" s="2">
@@ -72662,10 +72657,10 @@
         <v>128</v>
       </c>
       <c r="L667" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M667" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="N667" t="s" s="2">
         <v>344</v>
@@ -72678,7 +72673,7 @@
       </c>
       <c r="Q667" s="2"/>
       <c r="R667" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="S667" t="s" s="2">
         <v>73</v>
@@ -72737,10 +72732,10 @@
     </row>
     <row r="668" hidden="true">
       <c r="A668" t="s" s="2">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B668" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C668" s="2"/>
       <c r="D668" t="s" s="2">
@@ -72839,10 +72834,10 @@
     </row>
     <row r="669" hidden="true">
       <c r="A669" t="s" s="2">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C669" s="2"/>
       <c r="D669" t="s" s="2">
@@ -72943,10 +72938,10 @@
     </row>
     <row r="670" hidden="true">
       <c r="A670" t="s" s="2">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B670" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C670" s="2"/>
       <c r="D670" t="s" s="2">
@@ -73047,10 +73042,10 @@
     </row>
     <row r="671" hidden="true">
       <c r="A671" t="s" s="2">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B671" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C671" s="2"/>
       <c r="D671" t="s" s="2">
@@ -73151,13 +73146,13 @@
     </row>
     <row r="672" hidden="true">
       <c r="A672" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B672" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C672" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D672" t="s" s="2">
         <v>73</v>
@@ -73220,7 +73215,7 @@
       </c>
       <c r="Y672" s="2"/>
       <c r="Z672" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA672" t="s" s="2">
         <v>73</v>
@@ -73255,10 +73250,10 @@
     </row>
     <row r="673" hidden="true">
       <c r="A673" t="s" s="2">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B673" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C673" s="2"/>
       <c r="D673" t="s" s="2">
@@ -73355,10 +73350,10 @@
     </row>
     <row r="674" hidden="true">
       <c r="A674" t="s" s="2">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B674" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C674" s="2"/>
       <c r="D674" t="s" s="2">
@@ -73457,10 +73452,10 @@
     </row>
     <row r="675" hidden="true">
       <c r="A675" t="s" s="2">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B675" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C675" s="2"/>
       <c r="D675" t="s" s="2">
@@ -73486,10 +73481,10 @@
         <v>128</v>
       </c>
       <c r="L675" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>344</v>
@@ -73502,7 +73497,7 @@
       </c>
       <c r="Q675" s="2"/>
       <c r="R675" t="s" s="2">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="S675" t="s" s="2">
         <v>73</v>
@@ -73561,10 +73556,10 @@
     </row>
     <row r="676" hidden="true">
       <c r="A676" t="s" s="2">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B676" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C676" s="2"/>
       <c r="D676" t="s" s="2">
@@ -73663,10 +73658,10 @@
     </row>
     <row r="677" hidden="true">
       <c r="A677" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B677" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C677" s="2"/>
       <c r="D677" t="s" s="2">
@@ -73767,10 +73762,10 @@
     </row>
     <row r="678" hidden="true">
       <c r="A678" t="s" s="2">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B678" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C678" s="2"/>
       <c r="D678" t="s" s="2">
@@ -73871,10 +73866,10 @@
     </row>
     <row r="679" hidden="true">
       <c r="A679" t="s" s="2">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B679" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C679" s="2"/>
       <c r="D679" t="s" s="2">
@@ -73975,13 +73970,13 @@
     </row>
     <row r="680" hidden="true">
       <c r="A680" t="s" s="2">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C680" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D680" t="s" s="2">
         <v>73</v>
@@ -74044,7 +74039,7 @@
       </c>
       <c r="Y680" s="2"/>
       <c r="Z680" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AA680" t="s" s="2">
         <v>73</v>
@@ -74079,10 +74074,10 @@
     </row>
     <row r="681" hidden="true">
       <c r="A681" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B681" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C681" s="2"/>
       <c r="D681" t="s" s="2">
@@ -74179,10 +74174,10 @@
     </row>
     <row r="682" hidden="true">
       <c r="A682" t="s" s="2">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B682" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C682" s="2"/>
       <c r="D682" t="s" s="2">
@@ -74281,10 +74276,10 @@
     </row>
     <row r="683" hidden="true">
       <c r="A683" t="s" s="2">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B683" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C683" s="2"/>
       <c r="D683" t="s" s="2">
@@ -74310,7 +74305,7 @@
         <v>128</v>
       </c>
       <c r="L683" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="M683" t="s" s="2">
         <v>343</v>
@@ -74326,7 +74321,7 @@
       </c>
       <c r="Q683" s="2"/>
       <c r="R683" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="S683" t="s" s="2">
         <v>73</v>
@@ -74385,10 +74380,10 @@
     </row>
     <row r="684" hidden="true">
       <c r="A684" t="s" s="2">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C684" s="2"/>
       <c r="D684" t="s" s="2">
@@ -74487,10 +74482,10 @@
     </row>
     <row r="685" hidden="true">
       <c r="A685" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B685" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C685" s="2"/>
       <c r="D685" t="s" s="2">
@@ -74591,10 +74586,10 @@
     </row>
     <row r="686" hidden="true">
       <c r="A686" t="s" s="2">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B686" t="s" s="2">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C686" s="2"/>
       <c r="D686" t="s" s="2">
@@ -74695,10 +74690,10 @@
     </row>
     <row r="687" hidden="true">
       <c r="A687" t="s" s="2">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C687" s="2"/>
       <c r="D687" t="s" s="2">
@@ -74799,13 +74794,13 @@
     </row>
     <row r="688" hidden="true">
       <c r="A688" t="s" s="2">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C688" t="s" s="2">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D688" t="s" s="2">
         <v>73</v>
@@ -74830,7 +74825,7 @@
         <v>140</v>
       </c>
       <c r="L688" t="s" s="2">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="M688" t="s" s="2">
         <v>335</v>
@@ -74868,7 +74863,7 @@
       </c>
       <c r="Y688" s="2"/>
       <c r="Z688" t="s" s="2">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="AA688" t="s" s="2">
         <v>73</v>
@@ -74903,13 +74898,13 @@
     </row>
     <row r="689" hidden="true">
       <c r="A689" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D689" t="s" s="2">
         <v>73</v>
@@ -74934,7 +74929,7 @@
         <v>140</v>
       </c>
       <c r="L689" t="s" s="2">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="M689" t="s" s="2">
         <v>335</v>
@@ -74972,7 +74967,7 @@
       </c>
       <c r="Y689" s="2"/>
       <c r="Z689" t="s" s="2">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="AA689" t="s" s="2">
         <v>73</v>
@@ -75007,10 +75002,10 @@
     </row>
     <row r="690" hidden="true">
       <c r="A690" t="s" s="2">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C690" s="2"/>
       <c r="D690" t="s" s="2">
@@ -75111,10 +75106,10 @@
     </row>
     <row r="691" hidden="true">
       <c r="A691" t="s" s="2">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B691" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C691" s="2"/>
       <c r="D691" t="s" s="2">
@@ -75140,16 +75135,16 @@
         <v>252</v>
       </c>
       <c r="L691" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="M691" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N691" t="s" s="2">
         <v>393</v>
       </c>
       <c r="O691" t="s" s="2">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="P691" t="s" s="2">
         <v>73</v>
@@ -75198,7 +75193,7 @@
         <v>73</v>
       </c>
       <c r="AF691" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AG691" t="s" s="2">
         <v>74</v>
@@ -75215,10 +75210,10 @@
     </row>
     <row r="692" hidden="true">
       <c r="A692" t="s" s="2">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B692" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C692" s="2"/>
       <c r="D692" t="s" s="2">
@@ -75244,13 +75239,13 @@
         <v>397</v>
       </c>
       <c r="L692" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M692" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="N692" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="M692" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="N692" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="O692" s="2"/>
       <c r="P692" t="s" s="2">
@@ -75300,7 +75295,7 @@
         <v>73</v>
       </c>
       <c r="AF692" t="s" s="2">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AG692" t="s" s="2">
         <v>74</v>
@@ -75317,10 +75312,10 @@
     </row>
     <row r="693" hidden="true">
       <c r="A693" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C693" s="2"/>
       <c r="D693" t="s" s="2">
@@ -75343,19 +75338,19 @@
         <v>73</v>
       </c>
       <c r="K693" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="L693" t="s" s="2">
+        <v>1246</v>
+      </c>
+      <c r="M693" t="s" s="2">
         <v>1247</v>
       </c>
-      <c r="L693" t="s" s="2">
+      <c r="N693" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O693" t="s" s="2">
         <v>1248</v>
-      </c>
-      <c r="M693" t="s" s="2">
-        <v>1249</v>
-      </c>
-      <c r="N693" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O693" t="s" s="2">
-        <v>1250</v>
       </c>
       <c r="P693" t="s" s="2">
         <v>73</v>
@@ -75384,7 +75379,7 @@
       </c>
       <c r="Y693" s="2"/>
       <c r="Z693" t="s" s="2">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="AA693" t="s" s="2">
         <v>73</v>
@@ -75402,7 +75397,7 @@
         <v>73</v>
       </c>
       <c r="AF693" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="AG693" t="s" s="2">
         <v>74</v>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1033,7 +1033,8 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1299,8 +1300,7 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+    <t>Description of identifier</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -15457,7 +15457,7 @@
         <v>323</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="M111" t="s" s="2">
         <v>325</v>
@@ -17511,7 +17511,7 @@
         <v>323</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>325</v>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -19246,7 +19246,7 @@
         <v>74</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -20170,7 +20170,7 @@
         <v>74</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
@@ -22636,7 +22636,7 @@
         <v>74</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>73</v>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/main/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22466" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22466" uniqueCount="1251">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3025,426 +3025,424 @@
     <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession</t>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
+  </si>
+  <si>
+    <t>categorieProfession</t>
+  </si>
+  <si>
+    <t>Catégorie professionnelle indiquant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
   </si>
   <si>
     <t>profession</t>
   </si>
   <si>
-    <t>profession : Profession exercée ou future profession de l'étudiant.
-categorieProfessionnelle : Indique si le professionnel exerce sa profession en tant que :
-M: Militaire
-C: Civil
-F: Fonctionnaire
-E: Etudiant</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:categorieProfession</t>
-  </si>
-  <si>
-    <t>categorieProfession</t>
-  </si>
-  <si>
-    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:profession</t>
-  </si>
-  <si>
     <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J106-EnsembleProfession-RASS/FHIR/JDV-J106-EnsembleProfession-RASS</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.start</t>
+    <t>Practitioner.qualification:exercicePro.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.period.end</t>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
   </si>
   <si>
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.issuer</t>
+    <t>Practitioner.qualification:exercicePro.issuer</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire</t>
@@ -49896,7 +49894,7 @@
         <v>74</v>
       </c>
       <c r="G446" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H446" t="s" s="2">
         <v>73</v>
@@ -50720,7 +50718,7 @@
         <v>74</v>
       </c>
       <c r="G454" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H454" t="s" s="2">
         <v>73</v>
@@ -51544,7 +51542,7 @@
         <v>74</v>
       </c>
       <c r="G462" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H462" t="s" s="2">
         <v>73</v>
@@ -52368,7 +52366,7 @@
         <v>74</v>
       </c>
       <c r="G470" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H470" t="s" s="2">
         <v>73</v>
@@ -53192,7 +53190,7 @@
         <v>74</v>
       </c>
       <c r="G478" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H478" t="s" s="2">
         <v>73</v>
@@ -54016,7 +54014,7 @@
         <v>74</v>
       </c>
       <c r="G486" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H486" t="s" s="2">
         <v>73</v>
@@ -54840,7 +54838,7 @@
         <v>74</v>
       </c>
       <c r="G494" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H494" t="s" s="2">
         <v>73</v>
@@ -55664,7 +55662,7 @@
         <v>74</v>
       </c>
       <c r="G502" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H502" t="s" s="2">
         <v>73</v>
@@ -56488,7 +56486,7 @@
         <v>74</v>
       </c>
       <c r="G510" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H510" t="s" s="2">
         <v>73</v>
@@ -57312,7 +57310,7 @@
         <v>74</v>
       </c>
       <c r="G518" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H518" t="s" s="2">
         <v>73</v>
@@ -58136,7 +58134,7 @@
         <v>74</v>
       </c>
       <c r="G526" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H526" t="s" s="2">
         <v>73</v>
@@ -58960,7 +58958,7 @@
         <v>74</v>
       </c>
       <c r="G534" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H534" t="s" s="2">
         <v>73</v>
@@ -59784,7 +59782,7 @@
         <v>74</v>
       </c>
       <c r="G542" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H542" t="s" s="2">
         <v>73</v>
@@ -60608,7 +60606,7 @@
         <v>74</v>
       </c>
       <c r="G550" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H550" t="s" s="2">
         <v>73</v>
@@ -61526,7 +61524,7 @@
         <v>650</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>973</v>
+        <v>1100</v>
       </c>
       <c r="D559" t="s" s="2">
         <v>73</v>
@@ -61551,7 +61549,7 @@
         <v>140</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="M559" t="s" s="2">
         <v>335</v>
@@ -61589,7 +61587,7 @@
       </c>
       <c r="Y559" s="2"/>
       <c r="Z559" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AA559" t="s" s="2">
         <v>73</v>
@@ -61624,7 +61622,7 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>814</v>
@@ -61728,7 +61726,7 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>815</v>
@@ -61832,7 +61830,7 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B562" t="s" s="2">
         <v>960</v>
@@ -61932,7 +61930,7 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B563" t="s" s="2">
         <v>962</v>
@@ -62034,7 +62032,7 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B564" t="s" s="2">
         <v>964</v>
@@ -62063,7 +62061,7 @@
         <v>259</v>
       </c>
       <c r="L564" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="M564" t="s" s="2">
         <v>261</v>
@@ -62136,7 +62134,7 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B565" t="s" s="2">
         <v>967</v>
@@ -62165,7 +62163,7 @@
         <v>259</v>
       </c>
       <c r="L565" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="M565" t="s" s="2">
         <v>268</v>
@@ -62240,7 +62238,7 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B566" t="s" s="2">
         <v>819</v>
@@ -62342,13 +62340,13 @@
     </row>
     <row r="567" hidden="true">
       <c r="A567" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B567" t="s" s="2">
         <v>626</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D567" t="s" s="2">
         <v>73</v>
@@ -62373,7 +62371,7 @@
         <v>627</v>
       </c>
       <c r="L567" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="M567" t="s" s="2">
         <v>629</v>
@@ -62444,7 +62442,7 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B568" t="s" s="2">
         <v>631</v>
@@ -62544,7 +62542,7 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B569" t="s" s="2">
         <v>632</v>
@@ -62646,7 +62644,7 @@
     </row>
     <row r="570" hidden="true">
       <c r="A570" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B570" t="s" s="2">
         <v>633</v>
@@ -62750,7 +62748,7 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B571" t="s" s="2">
         <v>638</v>
@@ -62852,7 +62850,7 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B572" t="s" s="2">
         <v>642</v>
@@ -62954,7 +62952,7 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B573" t="s" s="2">
         <v>648</v>
@@ -63054,7 +63052,7 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B574" t="s" s="2">
         <v>649</v>
@@ -63156,7 +63154,7 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B575" t="s" s="2">
         <v>650</v>
@@ -63258,7 +63256,7 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B576" t="s" s="2">
         <v>650</v>
@@ -63274,7 +63272,7 @@
         <v>74</v>
       </c>
       <c r="G576" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H576" t="s" s="2">
         <v>73</v>
@@ -63362,7 +63360,7 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B577" t="s" s="2">
         <v>656</v>
@@ -63462,7 +63460,7 @@
     </row>
     <row r="578" hidden="true">
       <c r="A578" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B578" t="s" s="2">
         <v>658</v>
@@ -63564,7 +63562,7 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B579" t="s" s="2">
         <v>660</v>
@@ -63668,7 +63666,7 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B580" t="s" s="2">
         <v>664</v>
@@ -63770,7 +63768,7 @@
     </row>
     <row r="581" hidden="true">
       <c r="A581" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B581" t="s" s="2">
         <v>666</v>
@@ -63874,7 +63872,7 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B582" t="s" s="2">
         <v>668</v>
@@ -63978,7 +63976,7 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B583" t="s" s="2">
         <v>670</v>
@@ -64082,7 +64080,7 @@
     </row>
     <row r="584" hidden="true">
       <c r="A584" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B584" t="s" s="2">
         <v>650</v>
@@ -64098,7 +64096,7 @@
         <v>74</v>
       </c>
       <c r="G584" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H584" t="s" s="2">
         <v>73</v>
@@ -64186,7 +64184,7 @@
     </row>
     <row r="585" hidden="true">
       <c r="A585" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B585" t="s" s="2">
         <v>656</v>
@@ -64286,7 +64284,7 @@
     </row>
     <row r="586" hidden="true">
       <c r="A586" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B586" t="s" s="2">
         <v>658</v>
@@ -64388,7 +64386,7 @@
     </row>
     <row r="587" hidden="true">
       <c r="A587" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B587" t="s" s="2">
         <v>660</v>
@@ -64492,7 +64490,7 @@
     </row>
     <row r="588" hidden="true">
       <c r="A588" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B588" t="s" s="2">
         <v>664</v>
@@ -64594,7 +64592,7 @@
     </row>
     <row r="589" hidden="true">
       <c r="A589" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B589" t="s" s="2">
         <v>666</v>
@@ -64698,7 +64696,7 @@
     </row>
     <row r="590" hidden="true">
       <c r="A590" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B590" t="s" s="2">
         <v>668</v>
@@ -64802,7 +64800,7 @@
     </row>
     <row r="591" hidden="true">
       <c r="A591" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B591" t="s" s="2">
         <v>670</v>
@@ -64906,7 +64904,7 @@
     </row>
     <row r="592" hidden="true">
       <c r="A592" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B592" t="s" s="2">
         <v>650</v>
@@ -64922,7 +64920,7 @@
         <v>74</v>
       </c>
       <c r="G592" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H592" t="s" s="2">
         <v>73</v>
@@ -65010,7 +65008,7 @@
     </row>
     <row r="593" hidden="true">
       <c r="A593" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B593" t="s" s="2">
         <v>656</v>
@@ -65110,7 +65108,7 @@
     </row>
     <row r="594" hidden="true">
       <c r="A594" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B594" t="s" s="2">
         <v>658</v>
@@ -65212,7 +65210,7 @@
     </row>
     <row r="595" hidden="true">
       <c r="A595" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B595" t="s" s="2">
         <v>660</v>
@@ -65316,7 +65314,7 @@
     </row>
     <row r="596" hidden="true">
       <c r="A596" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B596" t="s" s="2">
         <v>664</v>
@@ -65418,7 +65416,7 @@
     </row>
     <row r="597" hidden="true">
       <c r="A597" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B597" t="s" s="2">
         <v>666</v>
@@ -65522,7 +65520,7 @@
     </row>
     <row r="598" hidden="true">
       <c r="A598" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B598" t="s" s="2">
         <v>668</v>
@@ -65626,7 +65624,7 @@
     </row>
     <row r="599" hidden="true">
       <c r="A599" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B599" t="s" s="2">
         <v>670</v>
@@ -65730,7 +65728,7 @@
     </row>
     <row r="600" hidden="true">
       <c r="A600" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B600" t="s" s="2">
         <v>650</v>
@@ -65746,7 +65744,7 @@
         <v>74</v>
       </c>
       <c r="G600" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H600" t="s" s="2">
         <v>73</v>
@@ -65834,7 +65832,7 @@
     </row>
     <row r="601" hidden="true">
       <c r="A601" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B601" t="s" s="2">
         <v>656</v>
@@ -65934,7 +65932,7 @@
     </row>
     <row r="602" hidden="true">
       <c r="A602" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B602" t="s" s="2">
         <v>658</v>
@@ -66036,7 +66034,7 @@
     </row>
     <row r="603" hidden="true">
       <c r="A603" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B603" t="s" s="2">
         <v>660</v>
@@ -66140,7 +66138,7 @@
     </row>
     <row r="604" hidden="true">
       <c r="A604" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B604" t="s" s="2">
         <v>664</v>
@@ -66242,7 +66240,7 @@
     </row>
     <row r="605" hidden="true">
       <c r="A605" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B605" t="s" s="2">
         <v>666</v>
@@ -66346,7 +66344,7 @@
     </row>
     <row r="606" hidden="true">
       <c r="A606" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B606" t="s" s="2">
         <v>668</v>
@@ -66450,7 +66448,7 @@
     </row>
     <row r="607" hidden="true">
       <c r="A607" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B607" t="s" s="2">
         <v>670</v>
@@ -66554,7 +66552,7 @@
     </row>
     <row r="608" hidden="true">
       <c r="A608" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B608" t="s" s="2">
         <v>650</v>
@@ -66570,7 +66568,7 @@
         <v>74</v>
       </c>
       <c r="G608" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H608" t="s" s="2">
         <v>73</v>
@@ -66658,7 +66656,7 @@
     </row>
     <row r="609" hidden="true">
       <c r="A609" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B609" t="s" s="2">
         <v>656</v>
@@ -66758,7 +66756,7 @@
     </row>
     <row r="610" hidden="true">
       <c r="A610" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B610" t="s" s="2">
         <v>658</v>
@@ -66860,7 +66858,7 @@
     </row>
     <row r="611" hidden="true">
       <c r="A611" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B611" t="s" s="2">
         <v>660</v>
@@ -66964,7 +66962,7 @@
     </row>
     <row r="612" hidden="true">
       <c r="A612" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B612" t="s" s="2">
         <v>664</v>
@@ -67066,7 +67064,7 @@
     </row>
     <row r="613" hidden="true">
       <c r="A613" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B613" t="s" s="2">
         <v>666</v>
@@ -67170,7 +67168,7 @@
     </row>
     <row r="614" hidden="true">
       <c r="A614" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B614" t="s" s="2">
         <v>668</v>
@@ -67274,7 +67272,7 @@
     </row>
     <row r="615" hidden="true">
       <c r="A615" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B615" t="s" s="2">
         <v>670</v>
@@ -67378,7 +67376,7 @@
     </row>
     <row r="616" hidden="true">
       <c r="A616" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B616" t="s" s="2">
         <v>650</v>
@@ -67394,7 +67392,7 @@
         <v>74</v>
       </c>
       <c r="G616" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H616" t="s" s="2">
         <v>73</v>
@@ -67482,7 +67480,7 @@
     </row>
     <row r="617" hidden="true">
       <c r="A617" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B617" t="s" s="2">
         <v>656</v>
@@ -67582,7 +67580,7 @@
     </row>
     <row r="618" hidden="true">
       <c r="A618" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B618" t="s" s="2">
         <v>658</v>
@@ -67684,7 +67682,7 @@
     </row>
     <row r="619" hidden="true">
       <c r="A619" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B619" t="s" s="2">
         <v>660</v>
@@ -67788,7 +67786,7 @@
     </row>
     <row r="620" hidden="true">
       <c r="A620" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B620" t="s" s="2">
         <v>664</v>
@@ -67890,7 +67888,7 @@
     </row>
     <row r="621" hidden="true">
       <c r="A621" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B621" t="s" s="2">
         <v>666</v>
@@ -67994,7 +67992,7 @@
     </row>
     <row r="622" hidden="true">
       <c r="A622" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B622" t="s" s="2">
         <v>668</v>
@@ -68098,7 +68096,7 @@
     </row>
     <row r="623" hidden="true">
       <c r="A623" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B623" t="s" s="2">
         <v>670</v>
@@ -68202,7 +68200,7 @@
     </row>
     <row r="624" hidden="true">
       <c r="A624" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B624" t="s" s="2">
         <v>650</v>
@@ -68218,7 +68216,7 @@
         <v>74</v>
       </c>
       <c r="G624" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H624" t="s" s="2">
         <v>73</v>
@@ -68306,7 +68304,7 @@
     </row>
     <row r="625" hidden="true">
       <c r="A625" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B625" t="s" s="2">
         <v>656</v>
@@ -68406,7 +68404,7 @@
     </row>
     <row r="626" hidden="true">
       <c r="A626" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B626" t="s" s="2">
         <v>658</v>
@@ -68508,7 +68506,7 @@
     </row>
     <row r="627" hidden="true">
       <c r="A627" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B627" t="s" s="2">
         <v>660</v>
@@ -68612,7 +68610,7 @@
     </row>
     <row r="628" hidden="true">
       <c r="A628" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B628" t="s" s="2">
         <v>664</v>
@@ -68714,7 +68712,7 @@
     </row>
     <row r="629" hidden="true">
       <c r="A629" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B629" t="s" s="2">
         <v>666</v>
@@ -68818,7 +68816,7 @@
     </row>
     <row r="630" hidden="true">
       <c r="A630" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B630" t="s" s="2">
         <v>668</v>
@@ -68922,7 +68920,7 @@
     </row>
     <row r="631" hidden="true">
       <c r="A631" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B631" t="s" s="2">
         <v>670</v>
@@ -69026,7 +69024,7 @@
     </row>
     <row r="632" hidden="true">
       <c r="A632" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B632" t="s" s="2">
         <v>650</v>
@@ -69042,7 +69040,7 @@
         <v>74</v>
       </c>
       <c r="G632" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H632" t="s" s="2">
         <v>73</v>
@@ -69130,7 +69128,7 @@
     </row>
     <row r="633" hidden="true">
       <c r="A633" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B633" t="s" s="2">
         <v>656</v>
@@ -69230,7 +69228,7 @@
     </row>
     <row r="634" hidden="true">
       <c r="A634" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B634" t="s" s="2">
         <v>658</v>
@@ -69332,7 +69330,7 @@
     </row>
     <row r="635" hidden="true">
       <c r="A635" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B635" t="s" s="2">
         <v>660</v>
@@ -69436,7 +69434,7 @@
     </row>
     <row r="636" hidden="true">
       <c r="A636" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B636" t="s" s="2">
         <v>664</v>
@@ -69538,7 +69536,7 @@
     </row>
     <row r="637" hidden="true">
       <c r="A637" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B637" t="s" s="2">
         <v>666</v>
@@ -69642,7 +69640,7 @@
     </row>
     <row r="638" hidden="true">
       <c r="A638" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B638" t="s" s="2">
         <v>668</v>
@@ -69746,7 +69744,7 @@
     </row>
     <row r="639" hidden="true">
       <c r="A639" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B639" t="s" s="2">
         <v>670</v>
@@ -69850,7 +69848,7 @@
     </row>
     <row r="640" hidden="true">
       <c r="A640" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B640" t="s" s="2">
         <v>650</v>
@@ -69866,7 +69864,7 @@
         <v>74</v>
       </c>
       <c r="G640" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H640" t="s" s="2">
         <v>73</v>
@@ -69954,7 +69952,7 @@
     </row>
     <row r="641" hidden="true">
       <c r="A641" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B641" t="s" s="2">
         <v>656</v>
@@ -70054,7 +70052,7 @@
     </row>
     <row r="642" hidden="true">
       <c r="A642" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B642" t="s" s="2">
         <v>658</v>
@@ -70156,7 +70154,7 @@
     </row>
     <row r="643" hidden="true">
       <c r="A643" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B643" t="s" s="2">
         <v>660</v>
@@ -70260,7 +70258,7 @@
     </row>
     <row r="644" hidden="true">
       <c r="A644" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B644" t="s" s="2">
         <v>664</v>
@@ -70362,7 +70360,7 @@
     </row>
     <row r="645" hidden="true">
       <c r="A645" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B645" t="s" s="2">
         <v>666</v>
@@ -70466,7 +70464,7 @@
     </row>
     <row r="646" hidden="true">
       <c r="A646" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B646" t="s" s="2">
         <v>668</v>
@@ -70570,7 +70568,7 @@
     </row>
     <row r="647" hidden="true">
       <c r="A647" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B647" t="s" s="2">
         <v>670</v>
@@ -70674,7 +70672,7 @@
     </row>
     <row r="648" hidden="true">
       <c r="A648" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B648" t="s" s="2">
         <v>650</v>
@@ -70690,7 +70688,7 @@
         <v>74</v>
       </c>
       <c r="G648" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H648" t="s" s="2">
         <v>73</v>
@@ -70778,7 +70776,7 @@
     </row>
     <row r="649" hidden="true">
       <c r="A649" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B649" t="s" s="2">
         <v>656</v>
@@ -70878,7 +70876,7 @@
     </row>
     <row r="650" hidden="true">
       <c r="A650" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B650" t="s" s="2">
         <v>658</v>
@@ -70980,7 +70978,7 @@
     </row>
     <row r="651" hidden="true">
       <c r="A651" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B651" t="s" s="2">
         <v>660</v>
@@ -71084,7 +71082,7 @@
     </row>
     <row r="652" hidden="true">
       <c r="A652" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B652" t="s" s="2">
         <v>664</v>
@@ -71186,7 +71184,7 @@
     </row>
     <row r="653" hidden="true">
       <c r="A653" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B653" t="s" s="2">
         <v>666</v>
@@ -71290,7 +71288,7 @@
     </row>
     <row r="654" hidden="true">
       <c r="A654" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B654" t="s" s="2">
         <v>668</v>
@@ -71394,7 +71392,7 @@
     </row>
     <row r="655" hidden="true">
       <c r="A655" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B655" t="s" s="2">
         <v>670</v>
@@ -71498,7 +71496,7 @@
     </row>
     <row r="656" hidden="true">
       <c r="A656" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B656" t="s" s="2">
         <v>650</v>
@@ -71514,7 +71512,7 @@
         <v>74</v>
       </c>
       <c r="G656" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H656" t="s" s="2">
         <v>73</v>
@@ -71602,7 +71600,7 @@
     </row>
     <row r="657" hidden="true">
       <c r="A657" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B657" t="s" s="2">
         <v>656</v>
@@ -71702,7 +71700,7 @@
     </row>
     <row r="658" hidden="true">
       <c r="A658" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B658" t="s" s="2">
         <v>658</v>
@@ -71804,7 +71802,7 @@
     </row>
     <row r="659" hidden="true">
       <c r="A659" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B659" t="s" s="2">
         <v>660</v>
@@ -71908,7 +71906,7 @@
     </row>
     <row r="660" hidden="true">
       <c r="A660" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B660" t="s" s="2">
         <v>664</v>
@@ -72010,7 +72008,7 @@
     </row>
     <row r="661" hidden="true">
       <c r="A661" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B661" t="s" s="2">
         <v>666</v>
@@ -72114,7 +72112,7 @@
     </row>
     <row r="662" hidden="true">
       <c r="A662" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B662" t="s" s="2">
         <v>668</v>
@@ -72218,7 +72216,7 @@
     </row>
     <row r="663" hidden="true">
       <c r="A663" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B663" t="s" s="2">
         <v>670</v>
@@ -72322,7 +72320,7 @@
     </row>
     <row r="664" hidden="true">
       <c r="A664" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B664" t="s" s="2">
         <v>650</v>
@@ -72338,7 +72336,7 @@
         <v>74</v>
       </c>
       <c r="G664" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H664" t="s" s="2">
         <v>73</v>
@@ -72426,7 +72424,7 @@
     </row>
     <row r="665" hidden="true">
       <c r="A665" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B665" t="s" s="2">
         <v>656</v>
@@ -72526,7 +72524,7 @@
     </row>
     <row r="666" hidden="true">
       <c r="A666" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B666" t="s" s="2">
         <v>658</v>
@@ -72628,7 +72626,7 @@
     </row>
     <row r="667" hidden="true">
       <c r="A667" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B667" t="s" s="2">
         <v>660</v>
@@ -72732,7 +72730,7 @@
     </row>
     <row r="668" hidden="true">
       <c r="A668" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B668" t="s" s="2">
         <v>664</v>
@@ -72834,7 +72832,7 @@
     </row>
     <row r="669" hidden="true">
       <c r="A669" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B669" t="s" s="2">
         <v>666</v>
@@ -72938,7 +72936,7 @@
     </row>
     <row r="670" hidden="true">
       <c r="A670" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B670" t="s" s="2">
         <v>668</v>
@@ -73042,7 +73040,7 @@
     </row>
     <row r="671" hidden="true">
       <c r="A671" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B671" t="s" s="2">
         <v>670</v>
@@ -73146,7 +73144,7 @@
     </row>
     <row r="672" hidden="true">
       <c r="A672" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B672" t="s" s="2">
         <v>650</v>
@@ -73162,7 +73160,7 @@
         <v>74</v>
       </c>
       <c r="G672" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H672" t="s" s="2">
         <v>73</v>
@@ -73250,7 +73248,7 @@
     </row>
     <row r="673" hidden="true">
       <c r="A673" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B673" t="s" s="2">
         <v>656</v>
@@ -73350,7 +73348,7 @@
     </row>
     <row r="674" hidden="true">
       <c r="A674" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B674" t="s" s="2">
         <v>658</v>
@@ -73452,7 +73450,7 @@
     </row>
     <row r="675" hidden="true">
       <c r="A675" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B675" t="s" s="2">
         <v>660</v>
@@ -73556,7 +73554,7 @@
     </row>
     <row r="676" hidden="true">
       <c r="A676" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B676" t="s" s="2">
         <v>664</v>
@@ -73658,7 +73656,7 @@
     </row>
     <row r="677" hidden="true">
       <c r="A677" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B677" t="s" s="2">
         <v>666</v>
@@ -73762,7 +73760,7 @@
     </row>
     <row r="678" hidden="true">
       <c r="A678" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B678" t="s" s="2">
         <v>668</v>
@@ -73866,7 +73864,7 @@
     </row>
     <row r="679" hidden="true">
       <c r="A679" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B679" t="s" s="2">
         <v>670</v>
@@ -73970,7 +73968,7 @@
     </row>
     <row r="680" hidden="true">
       <c r="A680" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B680" t="s" s="2">
         <v>650</v>
@@ -73986,7 +73984,7 @@
         <v>74</v>
       </c>
       <c r="G680" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H680" t="s" s="2">
         <v>73</v>
@@ -74074,7 +74072,7 @@
     </row>
     <row r="681" hidden="true">
       <c r="A681" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B681" t="s" s="2">
         <v>656</v>
@@ -74174,7 +74172,7 @@
     </row>
     <row r="682" hidden="true">
       <c r="A682" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B682" t="s" s="2">
         <v>658</v>
@@ -74276,7 +74274,7 @@
     </row>
     <row r="683" hidden="true">
       <c r="A683" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B683" t="s" s="2">
         <v>660</v>
@@ -74380,7 +74378,7 @@
     </row>
     <row r="684" hidden="true">
       <c r="A684" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B684" t="s" s="2">
         <v>664</v>
@@ -74482,7 +74480,7 @@
     </row>
     <row r="685" hidden="true">
       <c r="A685" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B685" t="s" s="2">
         <v>666</v>
@@ -74586,7 +74584,7 @@
     </row>
     <row r="686" hidden="true">
       <c r="A686" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B686" t="s" s="2">
         <v>668</v>
@@ -74690,7 +74688,7 @@
     </row>
     <row r="687" hidden="true">
       <c r="A687" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B687" t="s" s="2">
         <v>670</v>
@@ -74794,13 +74792,13 @@
     </row>
     <row r="688" hidden="true">
       <c r="A688" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>650</v>
       </c>
       <c r="C688" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D688" t="s" s="2">
         <v>73</v>
@@ -74825,7 +74823,7 @@
         <v>140</v>
       </c>
       <c r="L688" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="M688" t="s" s="2">
         <v>335</v>
@@ -74863,7 +74861,7 @@
       </c>
       <c r="Y688" s="2"/>
       <c r="Z688" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="AA688" t="s" s="2">
         <v>73</v>
@@ -74898,13 +74896,13 @@
     </row>
     <row r="689" hidden="true">
       <c r="A689" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>650</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D689" t="s" s="2">
         <v>73</v>
@@ -74929,7 +74927,7 @@
         <v>140</v>
       </c>
       <c r="L689" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="M689" t="s" s="2">
         <v>335</v>
@@ -74967,7 +74965,7 @@
       </c>
       <c r="Y689" s="2"/>
       <c r="Z689" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="AA689" t="s" s="2">
         <v>73</v>
@@ -75002,7 +75000,7 @@
     </row>
     <row r="690" hidden="true">
       <c r="A690" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>814</v>
@@ -75106,7 +75104,7 @@
     </row>
     <row r="691" hidden="true">
       <c r="A691" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>815</v>
@@ -75210,7 +75208,7 @@
     </row>
     <row r="692" hidden="true">
       <c r="A692" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>819</v>
@@ -75312,10 +75310,10 @@
     </row>
     <row r="693" hidden="true">
       <c r="A693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C693" s="2"/>
       <c r="D693" t="s" s="2">
@@ -75338,19 +75336,19 @@
         <v>73</v>
       </c>
       <c r="K693" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="L693" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="M693" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N693" t="s" s="2">
         <v>645</v>
       </c>
       <c r="O693" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="P693" t="s" s="2">
         <v>73</v>
@@ -75379,7 +75377,7 @@
       </c>
       <c r="Y693" s="2"/>
       <c r="Z693" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="AA693" t="s" s="2">
         <v>73</v>
@@ -75397,7 +75395,7 @@
         <v>73</v>
       </c>
       <c r="AF693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="AG693" t="s" s="2">
         <v>74</v>
